--- a/Generators/Experiment with utility data leak/diffusion_dataleak/3. Adult/TRTR_TSTR_results.xlsx
+++ b/Generators/Experiment with utility data leak/diffusion_dataleak/3. Adult/TRTR_TSTR_results.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="TRTR_Results" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="All_Comparisons" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="TabDDPM" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ForestDiffusion" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TRTR_Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All_Comparisons" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TabDDPM" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ForestDiffusion" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -522,639 +522,639 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>GradientBoost</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8385000000000001</v>
+        <v>0.525</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02582526755804176</v>
+        <v>0.05270462766947299</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8305541949820711</v>
+        <v>0.4933690349824439</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02852270307867011</v>
+        <v>0.05378629795968384</v>
       </c>
       <c r="F2" t="n">
-        <v>0.829281699641512</v>
+        <v>0.4829841867174139</v>
       </c>
       <c r="G2" t="n">
-        <v>0.02975094206425076</v>
+        <v>0.06111253566375451</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8385000000000001</v>
+        <v>0.525</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02582526755804176</v>
+        <v>0.05270462766947299</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.8385 ± 0.0258</t>
+          <t>0.5250 ± 0.0527</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.8306 ± 0.0285</t>
+          <t>0.4934 ± 0.0538</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.8293 ± 0.0298</t>
+          <t>0.4830 ± 0.0611</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.8385 ± 0.0258</t>
+          <t>0.5250 ± 0.0527</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.8385 ± 0.0258</t>
+          <t>0.5250 ± 0.0527</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.8306 ± 0.0285</t>
+          <t>0.4934 ± 0.0538</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.8293 ± 0.0298</t>
+          <t>0.4830 ± 0.0611</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0.8385 ± 0.0258</t>
+          <t>0.5250 ± 0.0527</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AdaBoost</t>
+          <t>SVM-RBF</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.837</v>
+        <v>0.515</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02335713072180646</v>
+        <v>0.04594682917363409</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8271380947617498</v>
+        <v>0.4010974358974359</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02698482468705257</v>
+        <v>0.05121627639470829</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8274717782384444</v>
+        <v>0.344789166784749</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02800542328232125</v>
+        <v>0.06757227328844036</v>
       </c>
       <c r="H3" t="n">
-        <v>0.837</v>
+        <v>0.515</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02335713072180646</v>
+        <v>0.04594682917363409</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.8370 ± 0.0234</t>
+          <t>0.5150 ± 0.0459</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.8271 ± 0.0270</t>
+          <t>0.4011 ± 0.0512</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.8275 ± 0.0280</t>
+          <t>0.3448 ± 0.0676</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.8370 ± 0.0234</t>
+          <t>0.5150 ± 0.0459</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.8370 ± 0.0234</t>
+          <t>0.5150 ± 0.0459</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.8271 ± 0.0270</t>
+          <t>0.4011 ± 0.0512</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.8275 ± 0.0280</t>
+          <t>0.3448 ± 0.0676</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>0.8370 ± 0.0234</t>
+          <t>0.5150 ± 0.0459</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SVM-RBF</t>
+          <t>AdaBoost</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8334999999999999</v>
+        <v>0.515</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01826502425706331</v>
+        <v>0.04887626099538394</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8099526079303931</v>
+        <v>0.4459274392015852</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02569511545306504</v>
+        <v>0.04904546419911374</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8244128167802897</v>
+        <v>0.4204506553904218</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02264298462168463</v>
+        <v>0.07436424082867353</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8334999999999999</v>
+        <v>0.515</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01826502425706331</v>
+        <v>0.04887626099538394</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.8335 ± 0.0183</t>
+          <t>0.5150 ± 0.0489</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.8100 ± 0.0257</t>
+          <t>0.4459 ± 0.0490</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.8244 ± 0.0226</t>
+          <t>0.4205 ± 0.0744</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.8335 ± 0.0183</t>
+          <t>0.5150 ± 0.0489</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.8335 ± 0.0183</t>
+          <t>0.5150 ± 0.0489</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.8100 ± 0.0257</t>
+          <t>0.4459 ± 0.0490</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.8244 ± 0.0226</t>
+          <t>0.4205 ± 0.0744</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.8335 ± 0.0183</t>
+          <t>0.5150 ± 0.0489</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GradientBoost</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.833</v>
+        <v>0.5049999999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0240601099101581</v>
+        <v>0.0483045891539648</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8246020797017092</v>
+        <v>0.3946722798843776</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02529261929811836</v>
+        <v>0.05058216691498373</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8239151747889606</v>
+        <v>0.3328350963552577</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02640491712024394</v>
+        <v>0.05354862018695906</v>
       </c>
       <c r="H5" t="n">
-        <v>0.833</v>
+        <v>0.5049999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0240601099101581</v>
+        <v>0.0483045891539648</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.8330 ± 0.0241</t>
+          <t>0.5050 ± 0.0483</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.8246 ± 0.0253</t>
+          <t>0.3947 ± 0.0506</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.8239 ± 0.0264</t>
+          <t>0.3328 ± 0.0535</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.8330 ± 0.0241</t>
+          <t>0.5050 ± 0.0483</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.8330 ± 0.0241</t>
+          <t>0.5050 ± 0.0483</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.8246 ± 0.0253</t>
+          <t>0.3947 ± 0.0506</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.8239 ± 0.0264</t>
+          <t>0.3328 ± 0.0535</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.8330 ± 0.0241</t>
+          <t>0.5050 ± 0.0483</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.828</v>
+        <v>0.4875</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02175622516277427</v>
+        <v>0.06373774391990981</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8104028939447145</v>
+        <v>0.4637476319006376</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02627109794847402</v>
+        <v>0.06802787926675574</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8146192868859166</v>
+        <v>0.4624339081811907</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02793976606486409</v>
+        <v>0.07612364353088311</v>
       </c>
       <c r="H6" t="n">
-        <v>0.828</v>
+        <v>0.4875</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02175622516277427</v>
+        <v>0.06373774391990981</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.8280 ± 0.0218</t>
+          <t>0.4875 ± 0.0637</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.8104 ± 0.0263</t>
+          <t>0.4637 ± 0.0680</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.8146 ± 0.0279</t>
+          <t>0.4624 ± 0.0761</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>0.8280 ± 0.0218</t>
+          <t>0.4875 ± 0.0637</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.8280 ± 0.0218</t>
+          <t>0.4875 ± 0.0637</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.8104 ± 0.0263</t>
+          <t>0.4637 ± 0.0680</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.8146 ± 0.0279</t>
+          <t>0.4624 ± 0.0761</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>0.8280 ± 0.0218</t>
+          <t>0.4875 ± 0.0637</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ExtraTrees</t>
+          <t>NaiveBayes</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8240000000000001</v>
+        <v>0.485</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02469817807045691</v>
+        <v>0.05797509043642027</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8177052906725901</v>
+        <v>0.3884614332892806</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02578592983226878</v>
+        <v>0.04926617125562362</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8164120745306315</v>
+        <v>0.3748825660014655</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02647286138062653</v>
+        <v>0.103253106459303</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8240000000000001</v>
+        <v>0.485</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02469817807045691</v>
+        <v>0.05797509043642027</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.8240 ± 0.0247</t>
+          <t>0.4850 ± 0.0580</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.8177 ± 0.0258</t>
+          <t>0.3885 ± 0.0493</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.8164 ± 0.0265</t>
+          <t>0.3749 ± 0.1033</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.8240 ± 0.0247</t>
+          <t>0.4850 ± 0.0580</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.8240 ± 0.0247</t>
+          <t>0.4850 ± 0.0580</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.8177 ± 0.0258</t>
+          <t>0.3885 ± 0.0493</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.8164 ± 0.0265</t>
+          <t>0.3749 ± 0.1033</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.8240 ± 0.0247</t>
+          <t>0.4850 ± 0.0580</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NaiveBayes</t>
+          <t>ExtraTrees</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8090000000000002</v>
+        <v>0.4774999999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02579836342785244</v>
+        <v>0.06503204338375557</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7856952309335539</v>
+        <v>0.4691265033149707</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02992064254649245</v>
+        <v>0.06795290437956898</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7897580695297388</v>
+        <v>0.4692555641821946</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03856477005414511</v>
+        <v>0.07472771724947783</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8090000000000002</v>
+        <v>0.4774999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02579836342785244</v>
+        <v>0.06503204338375557</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.8090 ± 0.0258</t>
+          <t>0.4775 ± 0.0650</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.7857 ± 0.0299</t>
+          <t>0.4691 ± 0.0680</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.7898 ± 0.0386</t>
+          <t>0.4693 ± 0.0747</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.8090 ± 0.0258</t>
+          <t>0.4775 ± 0.0650</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.8090 ± 0.0258</t>
+          <t>0.4775 ± 0.0650</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.7857 ± 0.0299</t>
+          <t>0.4691 ± 0.0680</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.7898 ± 0.0386</t>
+          <t>0.4693 ± 0.0747</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.8090 ± 0.0258</t>
+          <t>0.4775 ± 0.0650</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MLP</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8074999999999999</v>
+        <v>0.4699999999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02552232138518923</v>
+        <v>0.07799572637865058</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8069554910760722</v>
+        <v>0.4464738356606046</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02380568201797918</v>
+        <v>0.07281623112317112</v>
       </c>
       <c r="F9" t="n">
-        <v>0.808348378171001</v>
+        <v>0.4380473084886128</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02217982684553994</v>
+        <v>0.08049181275833353</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8074999999999999</v>
+        <v>0.4699999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02552232138518923</v>
+        <v>0.07799572637865058</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.8075 ± 0.0255</t>
+          <t>0.4700 ± 0.0780</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.8070 ± 0.0238</t>
+          <t>0.4465 ± 0.0728</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.8083 ± 0.0222</t>
+          <t>0.4380 ± 0.0805</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.8075 ± 0.0255</t>
+          <t>0.4700 ± 0.0780</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.8075 ± 0.0255</t>
+          <t>0.4700 ± 0.0780</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.8070 ± 0.0238</t>
+          <t>0.4465 ± 0.0728</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.8083 ± 0.0222</t>
+          <t>0.4380 ± 0.0805</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.8075 ± 0.0255</t>
+          <t>0.4700 ± 0.0780</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>MLP</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8069999999999998</v>
+        <v>0.4275</v>
       </c>
       <c r="C10" t="n">
-        <v>0.02250925735484548</v>
+        <v>0.05945352993912324</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8008786340418022</v>
+        <v>0.420859292671839</v>
       </c>
       <c r="E10" t="n">
-        <v>0.02509907434611157</v>
+        <v>0.0582664427371178</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7978462200616508</v>
+        <v>0.4272267905705405</v>
       </c>
       <c r="G10" t="n">
-        <v>0.02661462081347623</v>
+        <v>0.06077100676915963</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8069999999999998</v>
+        <v>0.4275</v>
       </c>
       <c r="I10" t="n">
-        <v>0.02250925735484548</v>
+        <v>0.05945352993912324</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.8070 ± 0.0225</t>
+          <t>0.4275 ± 0.0595</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.8009 ± 0.0251</t>
+          <t>0.4209 ± 0.0583</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.7978 ± 0.0266</t>
+          <t>0.4272 ± 0.0608</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.8070 ± 0.0225</t>
+          <t>0.4275 ± 0.0595</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.8070 ± 0.0225</t>
+          <t>0.4275 ± 0.0595</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.8009 ± 0.0251</t>
+          <t>0.4209 ± 0.0583</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.7978 ± 0.0266</t>
+          <t>0.4272 ± 0.0608</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.8070 ± 0.0225</t>
+          <t>0.4275 ± 0.0595</t>
         </is>
       </c>
     </row>
@@ -1165,67 +1165,67 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.784</v>
+        <v>0.4175</v>
       </c>
       <c r="C11" t="n">
-        <v>0.02913569784454954</v>
+        <v>0.0601502747753953</v>
       </c>
       <c r="D11" t="n">
-        <v>0.785293092246484</v>
+        <v>0.4187416830432881</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02860525768452616</v>
+        <v>0.05976891793014379</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7880825733490411</v>
+        <v>0.4405900453712953</v>
       </c>
       <c r="G11" t="n">
-        <v>0.02887004930408354</v>
+        <v>0.06784141632447085</v>
       </c>
       <c r="H11" t="n">
-        <v>0.784</v>
+        <v>0.4175</v>
       </c>
       <c r="I11" t="n">
-        <v>0.02913569784454954</v>
+        <v>0.0601502747753953</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.7840 ± 0.0291</t>
+          <t>0.4175 ± 0.0602</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.7853 ± 0.0286</t>
+          <t>0.4187 ± 0.0598</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.7881 ± 0.0289</t>
+          <t>0.4406 ± 0.0678</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.7840 ± 0.0291</t>
+          <t>0.4175 ± 0.0602</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.7840 ± 0.0291</t>
+          <t>0.4175 ± 0.0602</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.7853 ± 0.0286</t>
+          <t>0.4187 ± 0.0598</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.7881 ± 0.0289</t>
+          <t>0.4406 ± 0.0678</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.7840 ± 0.0291</t>
+          <t>0.4175 ± 0.0602</t>
         </is>
       </c>
     </row>
@@ -1438,148 +1438,148 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>GradientBoost</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8385000000000001</v>
+        <v>0.525</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02582526755804176</v>
+        <v>0.05270462766947299</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8305541949820711</v>
+        <v>0.4933690349824439</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02852270307867011</v>
+        <v>0.05378629795968384</v>
       </c>
       <c r="F2" t="n">
-        <v>0.829281699641512</v>
+        <v>0.4829841867174139</v>
       </c>
       <c r="G2" t="n">
-        <v>0.02975094206425076</v>
+        <v>0.06111253566375451</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8385000000000001</v>
+        <v>0.525</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02582526755804176</v>
+        <v>0.05270462766947299</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.8385 ± 0.0258</t>
+          <t>0.5250 ± 0.0527</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.8306 ± 0.0285</t>
+          <t>0.4934 ± 0.0538</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.8293 ± 0.0298</t>
+          <t>0.4830 ± 0.0611</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.8385 ± 0.0258</t>
+          <t>0.5250 ± 0.0527</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.8385 ± 0.0258</t>
+          <t>0.5250 ± 0.0527</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.8306 ± 0.0285</t>
+          <t>0.4934 ± 0.0538</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.8293 ± 0.0298</t>
+          <t>0.4830 ± 0.0611</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0.8385 ± 0.0258</t>
+          <t>0.5250 ± 0.0527</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>0.5125</v>
+        <v>0.3875</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1123795651649652</v>
+        <v>0.08599903100229286</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5395203310251679</v>
+        <v>0.3025445867729023</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1034656199890816</v>
+        <v>0.06458889472210863</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6429581736983061</v>
+        <v>0.2871417705278</v>
       </c>
       <c r="W2" t="n">
-        <v>0.04306004027927952</v>
+        <v>0.0545974671428285</v>
       </c>
       <c r="X2" t="n">
-        <v>0.5125</v>
+        <v>0.3875</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1123795651649652</v>
+        <v>0.08599903100229286</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.5125 ± 0.1124</t>
+          <t>0.3875 ± 0.0860</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.5395 ± 0.1035</t>
+          <t>0.3025 ± 0.0646</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.6430 ± 0.0431</t>
+          <t>0.2871 ± 0.0546</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0.5125 ± 0.1124</t>
+          <t>0.3875 ± 0.0860</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0.5125 ± 0.1124</t>
+          <t>0.3875 ± 0.0860</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>0.5395 ± 0.1035</t>
+          <t>0.3025 ± 0.0646</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.6430 ± 0.0431</t>
+          <t>0.2871 ± 0.0546</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.5125 ± 0.1124</t>
+          <t>0.3875 ± 0.0860</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>0.3260000000000002</v>
+        <v>0.1375000000000001</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.2910338639569031</v>
+        <v>0.1908244482095416</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.1863235259432059</v>
+        <v>0.1958424161896139</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.3260000000000002</v>
+        <v>0.1375000000000001</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1590,148 +1590,148 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AdaBoost</t>
+          <t>SVM-RBF</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.837</v>
+        <v>0.515</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02335713072180646</v>
+        <v>0.04594682917363409</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8271380947617498</v>
+        <v>0.4010974358974359</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02698482468705257</v>
+        <v>0.05121627639470829</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8274717782384444</v>
+        <v>0.344789166784749</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02800542328232125</v>
+        <v>0.06757227328844036</v>
       </c>
       <c r="H3" t="n">
-        <v>0.837</v>
+        <v>0.515</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02335713072180646</v>
+        <v>0.04594682917363409</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.8370 ± 0.0234</t>
+          <t>0.5150 ± 0.0459</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.8271 ± 0.0270</t>
+          <t>0.4011 ± 0.0512</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.8275 ± 0.0280</t>
+          <t>0.3448 ± 0.0676</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.8370 ± 0.0234</t>
+          <t>0.5150 ± 0.0459</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.8370 ± 0.0234</t>
+          <t>0.5150 ± 0.0459</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.8271 ± 0.0270</t>
+          <t>0.4011 ± 0.0512</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.8275 ± 0.0280</t>
+          <t>0.3448 ± 0.0676</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>0.8370 ± 0.0234</t>
+          <t>0.5150 ± 0.0459</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>0.5305000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1057368326449104</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5488756106178502</v>
+        <v>0.1</v>
       </c>
       <c r="U3" t="n">
-        <v>0.07559652370376714</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6271948053271059</v>
+        <v>0.0625</v>
       </c>
       <c r="W3" t="n">
-        <v>0.05744903576928705</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.5305000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1057368326449104</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.5305 ± 0.1057</t>
+          <t>0.2500 ± 0.0000</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.5489 ± 0.0756</t>
+          <t>0.1000 ± 0.0000</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.6272 ± 0.0574</t>
+          <t>0.0625 ± 0.0000</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>0.5305 ± 0.1057</t>
+          <t>0.2500 ± 0.0000</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0.5305 ± 0.1057</t>
+          <t>0.2500 ± 0.0000</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>0.5489 ± 0.0756</t>
+          <t>0.1000 ± 0.0000</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.6272 ± 0.0574</t>
+          <t>0.0625 ± 0.0000</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.5305 ± 0.1057</t>
+          <t>0.2500 ± 0.0000</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>0.3064999999999999</v>
+        <v>0.265</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.2782624841438996</v>
+        <v>0.3010974358974359</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.2002769729113385</v>
+        <v>0.282289166784749</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.3064999999999999</v>
+        <v>0.265</v>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
@@ -1742,148 +1742,148 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SVM-RBF</t>
+          <t>AdaBoost</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8334999999999999</v>
+        <v>0.515</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01826502425706331</v>
+        <v>0.04887626099538394</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8099526079303931</v>
+        <v>0.4459274392015852</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02569511545306504</v>
+        <v>0.04904546419911374</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8244128167802897</v>
+        <v>0.4204506553904218</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02264298462168463</v>
+        <v>0.07436424082867353</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8334999999999999</v>
+        <v>0.515</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01826502425706331</v>
+        <v>0.04887626099538394</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.8335 ± 0.0183</t>
+          <t>0.5150 ± 0.0489</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.8100 ± 0.0257</t>
+          <t>0.4459 ± 0.0490</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.8244 ± 0.0226</t>
+          <t>0.4205 ± 0.0744</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.8335 ± 0.0183</t>
+          <t>0.5150 ± 0.0489</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.8335 ± 0.0183</t>
+          <t>0.5150 ± 0.0489</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.8100 ± 0.0257</t>
+          <t>0.4459 ± 0.0490</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.8244 ± 0.0226</t>
+          <t>0.4205 ± 0.0744</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.8335 ± 0.0183</t>
+          <t>0.5150 ± 0.0489</t>
         </is>
       </c>
       <c r="R4" t="n">
-        <v>0.2305</v>
+        <v>0.26</v>
       </c>
       <c r="S4" t="n">
-        <v>0.008316649966583095</v>
+        <v>0.04116363011742822</v>
       </c>
       <c r="T4" t="n">
-        <v>0.09727722370394457</v>
+        <v>0.1614814135140222</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01464171707055061</v>
+        <v>0.06196347794844405</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5673248815657512</v>
+        <v>0.2553684824807116</v>
       </c>
       <c r="W4" t="n">
-        <v>0.3168651752883881</v>
+        <v>0.1394080724034463</v>
       </c>
       <c r="X4" t="n">
-        <v>0.2305</v>
+        <v>0.26</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.008316649966583095</v>
+        <v>0.04116363011742822</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.2305 ± 0.0083</t>
+          <t>0.2600 ± 0.0412</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.0973 ± 0.0146</t>
+          <t>0.1615 ± 0.0620</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.5673 ± 0.3169</t>
+          <t>0.2554 ± 0.1394</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.2305 ± 0.0083</t>
+          <t>0.2600 ± 0.0412</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0.2305 ± 0.0083</t>
+          <t>0.2600 ± 0.0412</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>0.0973 ± 0.0146</t>
+          <t>0.1615 ± 0.0620</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.5673 ± 0.3169</t>
+          <t>0.2554 ± 0.1394</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.2305 ± 0.0083</t>
+          <t>0.2600 ± 0.0412</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>0.6029999999999999</v>
+        <v>0.255</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.7126753842264486</v>
+        <v>0.2844460256875629</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.2570879352145384</v>
+        <v>0.1650821729097102</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.6029999999999999</v>
+        <v>0.255</v>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
@@ -1894,148 +1894,148 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GradientBoost</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.833</v>
+        <v>0.5049999999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0240601099101581</v>
+        <v>0.0483045891539648</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8246020797017092</v>
+        <v>0.3946722798843776</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02529261929811836</v>
+        <v>0.05058216691498373</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8239151747889606</v>
+        <v>0.3328350963552577</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02640491712024394</v>
+        <v>0.05354862018695906</v>
       </c>
       <c r="H5" t="n">
-        <v>0.833</v>
+        <v>0.5049999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0240601099101581</v>
+        <v>0.0483045891539648</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.8330 ± 0.0241</t>
+          <t>0.5050 ± 0.0483</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.8246 ± 0.0253</t>
+          <t>0.3947 ± 0.0506</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.8239 ± 0.0264</t>
+          <t>0.3328 ± 0.0535</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.8330 ± 0.0241</t>
+          <t>0.5050 ± 0.0483</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.8330 ± 0.0241</t>
+          <t>0.5050 ± 0.0483</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.8246 ± 0.0253</t>
+          <t>0.3947 ± 0.0506</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.8239 ± 0.0264</t>
+          <t>0.3328 ± 0.0535</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.8330 ± 0.0241</t>
+          <t>0.5050 ± 0.0483</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>0.3895</v>
+        <v>0.25</v>
       </c>
       <c r="S5" t="n">
-        <v>0.106860500965823</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4091344775251774</v>
+        <v>0.1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1220295067774568</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6031499807370405</v>
+        <v>0.0625</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1038495103829512</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3895</v>
+        <v>0.25</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.106860500965823</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.3895 ± 0.1069</t>
+          <t>0.2500 ± 0.0000</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.4091 ± 0.1220</t>
+          <t>0.1000 ± 0.0000</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.6031 ± 0.1038</t>
+          <t>0.0625 ± 0.0000</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.3895 ± 0.1069</t>
+          <t>0.2500 ± 0.0000</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0.3895 ± 0.1069</t>
+          <t>0.2500 ± 0.0000</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0.4091 ± 0.1220</t>
+          <t>0.1000 ± 0.0000</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.6031 ± 0.1038</t>
+          <t>0.0625 ± 0.0000</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.3895 ± 0.1069</t>
+          <t>0.2500 ± 0.0000</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>0.4435</v>
+        <v>0.2549999999999999</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.4154676021765318</v>
+        <v>0.2946722798843776</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.2207651940519201</v>
+        <v>0.2703350963552577</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.4435</v>
+        <v>0.2549999999999999</v>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
@@ -2046,148 +2046,148 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.828</v>
+        <v>0.4875</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02175622516277427</v>
+        <v>0.06373774391990981</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8104028939447145</v>
+        <v>0.4637476319006376</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02627109794847402</v>
+        <v>0.06802787926675574</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8146192868859166</v>
+        <v>0.4624339081811907</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02793976606486409</v>
+        <v>0.07612364353088311</v>
       </c>
       <c r="H6" t="n">
-        <v>0.828</v>
+        <v>0.4875</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02175622516277427</v>
+        <v>0.06373774391990981</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.8280 ± 0.0218</t>
+          <t>0.4875 ± 0.0637</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.8104 ± 0.0263</t>
+          <t>0.4637 ± 0.0680</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.8146 ± 0.0279</t>
+          <t>0.4624 ± 0.0761</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>0.8280 ± 0.0218</t>
+          <t>0.4875 ± 0.0637</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.8280 ± 0.0218</t>
+          <t>0.4875 ± 0.0637</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.8104 ± 0.0263</t>
+          <t>0.4637 ± 0.0680</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.8146 ± 0.0279</t>
+          <t>0.4624 ± 0.0761</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>0.8280 ± 0.0218</t>
+          <t>0.4875 ± 0.0637</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>0.2305</v>
+        <v>0.33</v>
       </c>
       <c r="S6" t="n">
-        <v>0.008316649966583095</v>
+        <v>0.0779957263786506</v>
       </c>
       <c r="T6" t="n">
-        <v>0.09727722370394457</v>
+        <v>0.2723531325719486</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01464171707055061</v>
+        <v>0.07142745007587166</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5673248815657512</v>
+        <v>0.2840750565457549</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3168651752883881</v>
+        <v>0.05686880834870454</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2305</v>
+        <v>0.33</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.008316649966583095</v>
+        <v>0.0779957263786506</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.2305 ± 0.0083</t>
+          <t>0.3300 ± 0.0780</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.0973 ± 0.0146</t>
+          <t>0.2724 ± 0.0714</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.5673 ± 0.3169</t>
+          <t>0.2841 ± 0.0569</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>0.2305 ± 0.0083</t>
+          <t>0.3300 ± 0.0780</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0.2305 ± 0.0083</t>
+          <t>0.3300 ± 0.0780</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>0.0973 ± 0.0146</t>
+          <t>0.2724 ± 0.0714</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.5673 ± 0.3169</t>
+          <t>0.2841 ± 0.0569</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>0.2305 ± 0.0083</t>
+          <t>0.3300 ± 0.0780</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>0.5974999999999999</v>
+        <v>0.1575</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.71312567024077</v>
+        <v>0.191394499328689</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.2472944053201653</v>
+        <v>0.1783588516354359</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.5974999999999999</v>
+        <v>0.1575</v>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
@@ -2198,148 +2198,148 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ExtraTrees</t>
+          <t>NaiveBayes</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8240000000000001</v>
+        <v>0.485</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02469817807045691</v>
+        <v>0.05797509043642027</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8177052906725901</v>
+        <v>0.3884614332892806</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02578592983226878</v>
+        <v>0.04926617125562362</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8164120745306315</v>
+        <v>0.3748825660014655</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02647286138062653</v>
+        <v>0.103253106459303</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8240000000000001</v>
+        <v>0.485</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02469817807045691</v>
+        <v>0.05797509043642027</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.8240 ± 0.0247</t>
+          <t>0.4850 ± 0.0580</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.8177 ± 0.0258</t>
+          <t>0.3885 ± 0.0493</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.8164 ± 0.0265</t>
+          <t>0.3749 ± 0.1033</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.8240 ± 0.0247</t>
+          <t>0.4850 ± 0.0580</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.8240 ± 0.0247</t>
+          <t>0.4850 ± 0.0580</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.8177 ± 0.0258</t>
+          <t>0.3885 ± 0.0493</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.8164 ± 0.0265</t>
+          <t>0.3749 ± 0.1033</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.8240 ± 0.0247</t>
+          <t>0.4850 ± 0.0580</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>0.5954999999999999</v>
+        <v>0.295</v>
       </c>
       <c r="S7" t="n">
-        <v>0.08725600902580355</v>
+        <v>0.07340905181848413</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6039978948807547</v>
+        <v>0.1753634781546781</v>
       </c>
       <c r="U7" t="n">
-        <v>0.05700630742689323</v>
+        <v>0.105704321437552</v>
       </c>
       <c r="V7" t="n">
-        <v>0.636558589265263</v>
+        <v>0.1773573523250943</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01581256914988814</v>
+        <v>0.1488571142648826</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5954999999999999</v>
+        <v>0.295</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.08725600902580355</v>
+        <v>0.07340905181848413</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.5955 ± 0.0873</t>
+          <t>0.2950 ± 0.0734</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.6040 ± 0.0570</t>
+          <t>0.1754 ± 0.1057</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.6366 ± 0.0158</t>
+          <t>0.1774 ± 0.1489</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>0.5955 ± 0.0873</t>
+          <t>0.2950 ± 0.0734</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0.5955 ± 0.0873</t>
+          <t>0.2950 ± 0.0734</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>0.6040 ± 0.0570</t>
+          <t>0.1754 ± 0.1057</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.6366 ± 0.0158</t>
+          <t>0.1774 ± 0.1489</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>0.5955 ± 0.0873</t>
+          <t>0.2950 ± 0.0734</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>0.2285000000000001</v>
+        <v>0.19</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.2137073957918354</v>
+        <v>0.2130979551346024</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.1798534852653685</v>
+        <v>0.1975252136763712</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.2285000000000001</v>
+        <v>0.19</v>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
@@ -2350,148 +2350,148 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NaiveBayes</t>
+          <t>ExtraTrees</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8090000000000002</v>
+        <v>0.4774999999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02579836342785244</v>
+        <v>0.06503204338375557</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7856952309335539</v>
+        <v>0.4691265033149707</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02992064254649245</v>
+        <v>0.06795290437956898</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7897580695297388</v>
+        <v>0.4692555641821946</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03856477005414511</v>
+        <v>0.07472771724947783</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8090000000000002</v>
+        <v>0.4774999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02579836342785244</v>
+        <v>0.06503204338375557</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.8090 ± 0.0258</t>
+          <t>0.4775 ± 0.0650</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.7857 ± 0.0299</t>
+          <t>0.4691 ± 0.0680</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.7898 ± 0.0386</t>
+          <t>0.4693 ± 0.0747</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.8090 ± 0.0258</t>
+          <t>0.4775 ± 0.0650</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.8090 ± 0.0258</t>
+          <t>0.4775 ± 0.0650</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.7857 ± 0.0299</t>
+          <t>0.4691 ± 0.0680</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.7898 ± 0.0386</t>
+          <t>0.4693 ± 0.0747</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.8090 ± 0.0258</t>
+          <t>0.4775 ± 0.0650</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>0.5655</v>
+        <v>0.3225</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1774268237267911</v>
+        <v>0.08032053840014326</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5443376427995192</v>
+        <v>0.2645316244756154</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1772402845995828</v>
+        <v>0.08099575491445819</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6655303303483318</v>
+        <v>0.2869117454018014</v>
       </c>
       <c r="W8" t="n">
-        <v>0.09270492416950747</v>
+        <v>0.08004562326683869</v>
       </c>
       <c r="X8" t="n">
-        <v>0.5655</v>
+        <v>0.3225</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.1774268237267911</v>
+        <v>0.08032053840014326</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.5655 ± 0.1774</t>
+          <t>0.3225 ± 0.0803</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.5443 ± 0.1772</t>
+          <t>0.2645 ± 0.0810</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.6655 ± 0.0927</t>
+          <t>0.2869 ± 0.0800</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>0.5655 ± 0.1774</t>
+          <t>0.3225 ± 0.0803</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0.5655 ± 0.1774</t>
+          <t>0.3225 ± 0.0803</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>0.5443 ± 0.1772</t>
+          <t>0.2645 ± 0.0810</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.6655 ± 0.0927</t>
+          <t>0.2869 ± 0.0800</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>0.5655 ± 0.1774</t>
+          <t>0.3225 ± 0.0803</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>0.2435000000000002</v>
+        <v>0.1549999999999999</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.2413575881340346</v>
+        <v>0.2045948788393553</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.1242277391814071</v>
+        <v>0.1823438187803932</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.2435000000000002</v>
+        <v>0.1549999999999999</v>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
@@ -2502,148 +2502,148 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MLP</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8074999999999999</v>
+        <v>0.4699999999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02552232138518923</v>
+        <v>0.07799572637865058</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8069554910760722</v>
+        <v>0.4464738356606046</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02380568201797918</v>
+        <v>0.07281623112317112</v>
       </c>
       <c r="F9" t="n">
-        <v>0.808348378171001</v>
+        <v>0.4380473084886128</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02217982684553994</v>
+        <v>0.08049181275833353</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8074999999999999</v>
+        <v>0.4699999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02552232138518923</v>
+        <v>0.07799572637865058</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.8075 ± 0.0255</t>
+          <t>0.4700 ± 0.0780</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.8070 ± 0.0238</t>
+          <t>0.4465 ± 0.0728</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.8083 ± 0.0222</t>
+          <t>0.4380 ± 0.0805</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.8075 ± 0.0255</t>
+          <t>0.4700 ± 0.0780</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.8075 ± 0.0255</t>
+          <t>0.4700 ± 0.0780</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.8070 ± 0.0238</t>
+          <t>0.4465 ± 0.0728</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.8083 ± 0.0222</t>
+          <t>0.4380 ± 0.0805</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.8075 ± 0.0255</t>
+          <t>0.4700 ± 0.0780</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>0.4575</v>
+        <v>0.3775000000000001</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2711933504592864</v>
+        <v>0.07587453093393358</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3571250032074406</v>
+        <v>0.3279301962087951</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2925635451498613</v>
+        <v>0.06211624669037222</v>
       </c>
       <c r="V9" t="n">
-        <v>0.4823265278645917</v>
+        <v>0.3122595904878523</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2529046991217041</v>
+        <v>0.05659514923852697</v>
       </c>
       <c r="X9" t="n">
-        <v>0.4575</v>
+        <v>0.3775000000000001</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.2711933504592864</v>
+        <v>0.07587453093393358</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.4575 ± 0.2712</t>
+          <t>0.3775 ± 0.0759</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.3571 ± 0.2926</t>
+          <t>0.3279 ± 0.0621</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.4823 ± 0.2529</t>
+          <t>0.3123 ± 0.0566</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0.4575 ± 0.2712</t>
+          <t>0.3775 ± 0.0759</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0.4575 ± 0.2712</t>
+          <t>0.3775 ± 0.0759</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>0.3571 ± 0.2926</t>
+          <t>0.3279 ± 0.0621</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.4823 ± 0.2529</t>
+          <t>0.3123 ± 0.0566</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>0.4575 ± 0.2712</t>
+          <t>0.3775 ± 0.0759</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>0.3499999999999999</v>
+        <v>0.09249999999999986</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.4498304878686316</v>
+        <v>0.1185436394518095</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.3260218503064093</v>
+        <v>0.1257877180007605</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.3499999999999999</v>
+        <v>0.09249999999999986</v>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
@@ -2654,148 +2654,148 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>MLP</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8069999999999998</v>
+        <v>0.4275</v>
       </c>
       <c r="C10" t="n">
-        <v>0.02250925735484548</v>
+        <v>0.05945352993912324</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8008786340418022</v>
+        <v>0.420859292671839</v>
       </c>
       <c r="E10" t="n">
-        <v>0.02509907434611157</v>
+        <v>0.0582664427371178</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7978462200616508</v>
+        <v>0.4272267905705405</v>
       </c>
       <c r="G10" t="n">
-        <v>0.02661462081347623</v>
+        <v>0.06077100676915963</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8069999999999998</v>
+        <v>0.4275</v>
       </c>
       <c r="I10" t="n">
-        <v>0.02250925735484548</v>
+        <v>0.05945352993912324</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.8070 ± 0.0225</t>
+          <t>0.4275 ± 0.0595</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.8009 ± 0.0251</t>
+          <t>0.4209 ± 0.0583</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.7978 ± 0.0266</t>
+          <t>0.4272 ± 0.0608</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.8070 ± 0.0225</t>
+          <t>0.4275 ± 0.0595</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.8070 ± 0.0225</t>
+          <t>0.4275 ± 0.0595</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.8009 ± 0.0251</t>
+          <t>0.4209 ± 0.0583</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.7978 ± 0.0266</t>
+          <t>0.4272 ± 0.0608</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.8070 ± 0.0225</t>
+          <t>0.4275 ± 0.0595</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>0.6029999999999999</v>
+        <v>0.295</v>
       </c>
       <c r="S10" t="n">
-        <v>0.06490163497341357</v>
+        <v>0.09486832980505137</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6279760268799872</v>
+        <v>0.1411864406779661</v>
       </c>
       <c r="U10" t="n">
-        <v>0.05528025871606659</v>
+        <v>0.0868286408385216</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6853656925276244</v>
+        <v>0.095125</v>
       </c>
       <c r="W10" t="n">
-        <v>0.02424663571614332</v>
+        <v>0.06877953910866226</v>
       </c>
       <c r="X10" t="n">
-        <v>0.6029999999999999</v>
+        <v>0.295</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.06490163497341357</v>
+        <v>0.09486832980505137</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.6030 ± 0.0649</t>
+          <t>0.2950 ± 0.0949</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.6280 ± 0.0553</t>
+          <t>0.1412 ± 0.0868</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.6854 ± 0.0242</t>
+          <t>0.0951 ± 0.0688</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>0.6030 ± 0.0649</t>
+          <t>0.2950 ± 0.0949</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0.6030 ± 0.0649</t>
+          <t>0.2950 ± 0.0949</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>0.6280 ± 0.0553</t>
+          <t>0.1412 ± 0.0868</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.6854 ± 0.0242</t>
+          <t>0.0951 ± 0.0688</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>0.6030 ± 0.0649</t>
+          <t>0.2950 ± 0.0949</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>0.204</v>
+        <v>0.1325</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.1729026071618149</v>
+        <v>0.2796728519938729</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.1124805275340265</v>
+        <v>0.3321017905705405</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.204</v>
+        <v>0.1325</v>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
@@ -2810,144 +2810,144 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.784</v>
+        <v>0.4175</v>
       </c>
       <c r="C11" t="n">
-        <v>0.02913569784454954</v>
+        <v>0.0601502747753953</v>
       </c>
       <c r="D11" t="n">
-        <v>0.785293092246484</v>
+        <v>0.4187416830432881</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02860525768452616</v>
+        <v>0.05976891793014379</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7880825733490411</v>
+        <v>0.4405900453712953</v>
       </c>
       <c r="G11" t="n">
-        <v>0.02887004930408354</v>
+        <v>0.06784141632447085</v>
       </c>
       <c r="H11" t="n">
-        <v>0.784</v>
+        <v>0.4175</v>
       </c>
       <c r="I11" t="n">
-        <v>0.02913569784454954</v>
+        <v>0.0601502747753953</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.7840 ± 0.0291</t>
+          <t>0.4175 ± 0.0602</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.7853 ± 0.0286</t>
+          <t>0.4187 ± 0.0598</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.7881 ± 0.0289</t>
+          <t>0.4406 ± 0.0678</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.7840 ± 0.0291</t>
+          <t>0.4175 ± 0.0602</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.7840 ± 0.0291</t>
+          <t>0.4175 ± 0.0602</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.7853 ± 0.0286</t>
+          <t>0.4187 ± 0.0598</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.7881 ± 0.0289</t>
+          <t>0.4406 ± 0.0678</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.7840 ± 0.0291</t>
+          <t>0.4175 ± 0.0602</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>0.533</v>
+        <v>0.325</v>
       </c>
       <c r="S11" t="n">
-        <v>0.08944893018427393</v>
+        <v>0.05651941652604389</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5585204539883526</v>
+        <v>0.2703054200272416</v>
       </c>
       <c r="U11" t="n">
-        <v>0.07763899105273228</v>
+        <v>0.0595591187161921</v>
       </c>
       <c r="V11" t="n">
-        <v>0.6609231821422814</v>
+        <v>0.2791311912544671</v>
       </c>
       <c r="W11" t="n">
-        <v>0.07338396495062781</v>
+        <v>0.06063250779160817</v>
       </c>
       <c r="X11" t="n">
-        <v>0.533</v>
+        <v>0.325</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.08944893018427393</v>
+        <v>0.05651941652604389</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.5330 ± 0.0894</t>
+          <t>0.3250 ± 0.0565</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.5585 ± 0.0776</t>
+          <t>0.2703 ± 0.0596</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.6609 ± 0.0734</t>
+          <t>0.2791 ± 0.0606</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>0.5330 ± 0.0894</t>
+          <t>0.3250 ± 0.0565</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0.5330 ± 0.0894</t>
+          <t>0.3250 ± 0.0565</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>0.5585 ± 0.0776</t>
+          <t>0.2703 ± 0.0596</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.6609 ± 0.0734</t>
+          <t>0.2791 ± 0.0606</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0.5330 ± 0.0894</t>
+          <t>0.3250 ± 0.0565</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>0.251</v>
+        <v>0.09249999999999997</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.2267726382581314</v>
+        <v>0.1484362630160465</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.1271593912067597</v>
+        <v>0.1614588541168283</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.251</v>
+        <v>0.09249999999999997</v>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
@@ -2958,148 +2958,148 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>GradientBoost</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8385000000000001</v>
+        <v>0.525</v>
       </c>
       <c r="C12" t="n">
-        <v>0.02582526755804176</v>
+        <v>0.05270462766947299</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8305541949820711</v>
+        <v>0.4933690349824439</v>
       </c>
       <c r="E12" t="n">
-        <v>0.02852270307867011</v>
+        <v>0.05378629795968384</v>
       </c>
       <c r="F12" t="n">
-        <v>0.829281699641512</v>
+        <v>0.4829841867174139</v>
       </c>
       <c r="G12" t="n">
-        <v>0.02975094206425076</v>
+        <v>0.06111253566375451</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8385000000000001</v>
+        <v>0.525</v>
       </c>
       <c r="I12" t="n">
-        <v>0.02582526755804176</v>
+        <v>0.05270462766947299</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.8385 ± 0.0258</t>
+          <t>0.5250 ± 0.0527</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.8306 ± 0.0285</t>
+          <t>0.4934 ± 0.0538</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0.8293 ± 0.0298</t>
+          <t>0.4830 ± 0.0611</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>0.8385 ± 0.0258</t>
+          <t>0.5250 ± 0.0527</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.8385 ± 0.0258</t>
+          <t>0.5250 ± 0.0527</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.8306 ± 0.0285</t>
+          <t>0.4934 ± 0.0538</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0.8293 ± 0.0298</t>
+          <t>0.4830 ± 0.0611</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0.8385 ± 0.0258</t>
+          <t>0.5250 ± 0.0527</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>0.7464999999999999</v>
+        <v>0.415</v>
       </c>
       <c r="S12" t="n">
-        <v>0.02068950351157698</v>
+        <v>0.04594682917363407</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7644637239952305</v>
+        <v>0.3702766543942891</v>
       </c>
       <c r="U12" t="n">
-        <v>0.01887158862533338</v>
+        <v>0.03913577841474109</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8155266283306348</v>
+        <v>0.3461739410138925</v>
       </c>
       <c r="W12" t="n">
-        <v>0.02103133590380068</v>
+        <v>0.04677190854226341</v>
       </c>
       <c r="X12" t="n">
-        <v>0.7464999999999999</v>
+        <v>0.415</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.02068950351157698</v>
+        <v>0.04594682917363407</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.7465 ± 0.0207</t>
+          <t>0.4150 ± 0.0459</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.7645 ± 0.0189</t>
+          <t>0.3703 ± 0.0391</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.8155 ± 0.0210</t>
+          <t>0.3462 ± 0.0468</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>0.7465 ± 0.0207</t>
+          <t>0.4150 ± 0.0459</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>0.7465 ± 0.0207</t>
+          <t>0.4150 ± 0.0459</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>0.7645 ± 0.0189</t>
+          <t>0.3703 ± 0.0391</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.8155 ± 0.0210</t>
+          <t>0.3462 ± 0.0468</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>0.7465 ± 0.0207</t>
+          <t>0.4150 ± 0.0459</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>0.09200000000000019</v>
+        <v>0.11</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.06609047098684051</v>
+        <v>0.1230923805881548</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.01375507131087716</v>
+        <v>0.1368102457035213</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.09200000000000019</v>
+        <v>0.11</v>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
@@ -3110,148 +3110,148 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AdaBoost</t>
+          <t>SVM-RBF</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.837</v>
+        <v>0.515</v>
       </c>
       <c r="C13" t="n">
-        <v>0.02335713072180646</v>
+        <v>0.04594682917363409</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8271380947617498</v>
+        <v>0.4010974358974359</v>
       </c>
       <c r="E13" t="n">
-        <v>0.02698482468705257</v>
+        <v>0.05121627639470829</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8274717782384444</v>
+        <v>0.344789166784749</v>
       </c>
       <c r="G13" t="n">
-        <v>0.02800542328232125</v>
+        <v>0.06757227328844036</v>
       </c>
       <c r="H13" t="n">
-        <v>0.837</v>
+        <v>0.515</v>
       </c>
       <c r="I13" t="n">
-        <v>0.02335713072180646</v>
+        <v>0.04594682917363409</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.8370 ± 0.0234</t>
+          <t>0.5150 ± 0.0459</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.8271 ± 0.0270</t>
+          <t>0.4011 ± 0.0512</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0.8275 ± 0.0280</t>
+          <t>0.3448 ± 0.0676</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>0.8370 ± 0.0234</t>
+          <t>0.5150 ± 0.0459</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>0.8370 ± 0.0234</t>
+          <t>0.5150 ± 0.0459</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>0.8271 ± 0.0270</t>
+          <t>0.4011 ± 0.0512</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>0.8275 ± 0.0280</t>
+          <t>0.3448 ± 0.0676</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>0.8370 ± 0.0234</t>
+          <t>0.5150 ± 0.0459</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>0.728</v>
+        <v>0.3475</v>
       </c>
       <c r="S13" t="n">
-        <v>0.03216278042154384</v>
+        <v>0.05827377912349029</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7495993986021727</v>
+        <v>0.3189944749878827</v>
       </c>
       <c r="U13" t="n">
-        <v>0.02904182696431352</v>
+        <v>0.04955858690316203</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8274841147304658</v>
+        <v>0.3133261472009579</v>
       </c>
       <c r="W13" t="n">
-        <v>0.02375472961573071</v>
+        <v>0.04772700887846521</v>
       </c>
       <c r="X13" t="n">
-        <v>0.728</v>
+        <v>0.3475</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.03216278042154384</v>
+        <v>0.05827377912349029</v>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>0.7280 ± 0.0322</t>
+          <t>0.3475 ± 0.0583</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.7496 ± 0.0290</t>
+          <t>0.3190 ± 0.0496</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>0.8275 ± 0.0238</t>
+          <t>0.3133 ± 0.0477</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>0.7280 ± 0.0322</t>
+          <t>0.3475 ± 0.0583</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>0.7280 ± 0.0322</t>
+          <t>0.3475 ± 0.0583</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>0.7496 ± 0.0290</t>
+          <t>0.3190 ± 0.0496</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>0.8275 ± 0.0238</t>
+          <t>0.3133 ± 0.0477</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>0.7280 ± 0.0322</t>
+          <t>0.3475 ± 0.0583</t>
         </is>
       </c>
       <c r="AH13" t="n">
-        <v>0.109</v>
+        <v>0.1675</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.07753869615957709</v>
+        <v>0.08210296090955316</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-1.233649202136977e-05</v>
+        <v>0.03146301958379111</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.109</v>
+        <v>0.1675</v>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
@@ -3262,148 +3262,148 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SVM-RBF</t>
+          <t>AdaBoost</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8334999999999999</v>
+        <v>0.515</v>
       </c>
       <c r="C14" t="n">
-        <v>0.01826502425706331</v>
+        <v>0.04887626099538394</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8099526079303931</v>
+        <v>0.4459274392015852</v>
       </c>
       <c r="E14" t="n">
-        <v>0.02569511545306504</v>
+        <v>0.04904546419911374</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8244128167802897</v>
+        <v>0.4204506553904218</v>
       </c>
       <c r="G14" t="n">
-        <v>0.02264298462168463</v>
+        <v>0.07436424082867353</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8334999999999999</v>
+        <v>0.515</v>
       </c>
       <c r="I14" t="n">
-        <v>0.01826502425706331</v>
+        <v>0.04887626099538394</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.8335 ± 0.0183</t>
+          <t>0.5150 ± 0.0489</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.8100 ± 0.0257</t>
+          <t>0.4459 ± 0.0490</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0.8244 ± 0.0226</t>
+          <t>0.4205 ± 0.0744</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0.8335 ± 0.0183</t>
+          <t>0.5150 ± 0.0489</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.8335 ± 0.0183</t>
+          <t>0.5150 ± 0.0489</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.8100 ± 0.0257</t>
+          <t>0.4459 ± 0.0490</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.8244 ± 0.0226</t>
+          <t>0.4205 ± 0.0744</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0.8335 ± 0.0183</t>
+          <t>0.5150 ± 0.0489</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>0.7155</v>
+        <v>0.3625</v>
       </c>
       <c r="S14" t="n">
-        <v>0.02278522913351252</v>
+        <v>0.05432668671002207</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7382835601759095</v>
+        <v>0.3313916786357202</v>
       </c>
       <c r="U14" t="n">
-        <v>0.02057169283043969</v>
+        <v>0.04909575685811794</v>
       </c>
       <c r="V14" t="n">
-        <v>0.8183299333627895</v>
+        <v>0.3253566091869237</v>
       </c>
       <c r="W14" t="n">
-        <v>0.0154113579273181</v>
+        <v>0.05303249341597213</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7155</v>
+        <v>0.3625</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.02278522913351252</v>
+        <v>0.05432668671002207</v>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>0.7155 ± 0.0228</t>
+          <t>0.3625 ± 0.0543</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.7383 ± 0.0206</t>
+          <t>0.3314 ± 0.0491</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>0.8183 ± 0.0154</t>
+          <t>0.3254 ± 0.0530</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>0.7155 ± 0.0228</t>
+          <t>0.3625 ± 0.0543</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>0.7155 ± 0.0228</t>
+          <t>0.3625 ± 0.0543</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>0.7383 ± 0.0206</t>
+          <t>0.3314 ± 0.0491</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>0.8183 ± 0.0154</t>
+          <t>0.3254 ± 0.0530</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>0.7155 ± 0.0228</t>
+          <t>0.3625 ± 0.0543</t>
         </is>
       </c>
       <c r="AH14" t="n">
-        <v>0.1179999999999999</v>
+        <v>0.1525</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.07166904775448368</v>
+        <v>0.114535760565865</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.006082883417500184</v>
+        <v>0.09509404620349815</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.1179999999999999</v>
+        <v>0.1525</v>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
@@ -3414,148 +3414,148 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GradientBoost</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.833</v>
+        <v>0.5049999999999999</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0240601099101581</v>
+        <v>0.0483045891539648</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8246020797017092</v>
+        <v>0.3946722798843776</v>
       </c>
       <c r="E15" t="n">
-        <v>0.02529261929811836</v>
+        <v>0.05058216691498373</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8239151747889606</v>
+        <v>0.3328350963552577</v>
       </c>
       <c r="G15" t="n">
-        <v>0.02640491712024394</v>
+        <v>0.05354862018695906</v>
       </c>
       <c r="H15" t="n">
-        <v>0.833</v>
+        <v>0.5049999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0240601099101581</v>
+        <v>0.0483045891539648</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.8330 ± 0.0241</t>
+          <t>0.5050 ± 0.0483</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.8246 ± 0.0253</t>
+          <t>0.3947 ± 0.0506</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0.8239 ± 0.0264</t>
+          <t>0.3328 ± 0.0535</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>0.8330 ± 0.0241</t>
+          <t>0.5050 ± 0.0483</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0.8330 ± 0.0241</t>
+          <t>0.5050 ± 0.0483</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0.8246 ± 0.0253</t>
+          <t>0.3947 ± 0.0506</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0.8239 ± 0.0264</t>
+          <t>0.3328 ± 0.0535</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>0.8330 ± 0.0241</t>
+          <t>0.5050 ± 0.0483</t>
         </is>
       </c>
       <c r="R15" t="n">
-        <v>0.7785</v>
+        <v>0.3525</v>
       </c>
       <c r="S15" t="n">
-        <v>0.03894797099265179</v>
+        <v>0.06174544517614234</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7931164357496072</v>
+        <v>0.3235520526667839</v>
       </c>
       <c r="U15" t="n">
-        <v>0.03472767570107376</v>
+        <v>0.05209316108357043</v>
       </c>
       <c r="V15" t="n">
-        <v>0.8349204608807771</v>
+        <v>0.3151442410228081</v>
       </c>
       <c r="W15" t="n">
-        <v>0.02494069345512922</v>
+        <v>0.05026454564895595</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7785</v>
+        <v>0.3525</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.03894797099265179</v>
+        <v>0.06174544517614234</v>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>0.7785 ± 0.0389</t>
+          <t>0.3525 ± 0.0617</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.7931 ± 0.0347</t>
+          <t>0.3236 ± 0.0521</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>0.8349 ± 0.0249</t>
+          <t>0.3151 ± 0.0503</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>0.7785 ± 0.0389</t>
+          <t>0.3525 ± 0.0617</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>0.7785 ± 0.0389</t>
+          <t>0.3525 ± 0.0617</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>0.7931 ± 0.0347</t>
+          <t>0.3236 ± 0.0521</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>0.8349 ± 0.0249</t>
+          <t>0.3151 ± 0.0503</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>0.7785 ± 0.0389</t>
+          <t>0.3525 ± 0.0617</t>
         </is>
       </c>
       <c r="AH15" t="n">
-        <v>0.05449999999999999</v>
+        <v>0.1524999999999999</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.03148564395210196</v>
+        <v>0.0711202272175937</v>
       </c>
       <c r="AJ15" t="n">
-        <v>-0.0110052860918165</v>
+        <v>0.01769085533244952</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.05449999999999999</v>
+        <v>0.1524999999999999</v>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
@@ -3566,148 +3566,148 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.828</v>
+        <v>0.4875</v>
       </c>
       <c r="C16" t="n">
-        <v>0.02175622516277427</v>
+        <v>0.06373774391990981</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8104028939447145</v>
+        <v>0.4637476319006376</v>
       </c>
       <c r="E16" t="n">
-        <v>0.02627109794847402</v>
+        <v>0.06802787926675574</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8146192868859166</v>
+        <v>0.4624339081811907</v>
       </c>
       <c r="G16" t="n">
-        <v>0.02793976606486409</v>
+        <v>0.07612364353088311</v>
       </c>
       <c r="H16" t="n">
-        <v>0.828</v>
+        <v>0.4875</v>
       </c>
       <c r="I16" t="n">
-        <v>0.02175622516277427</v>
+        <v>0.06373774391990981</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.8280 ± 0.0218</t>
+          <t>0.4875 ± 0.0637</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0.8104 ± 0.0263</t>
+          <t>0.4637 ± 0.0680</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0.8146 ± 0.0279</t>
+          <t>0.4624 ± 0.0761</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>0.8280 ± 0.0218</t>
+          <t>0.4875 ± 0.0637</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>0.8280 ± 0.0218</t>
+          <t>0.4875 ± 0.0637</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>0.8104 ± 0.0263</t>
+          <t>0.4637 ± 0.0680</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>0.8146 ± 0.0279</t>
+          <t>0.4624 ± 0.0761</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>0.8280 ± 0.0218</t>
+          <t>0.4875 ± 0.0637</t>
         </is>
       </c>
       <c r="R16" t="n">
-        <v>0.7204999999999999</v>
+        <v>0.3875</v>
       </c>
       <c r="S16" t="n">
-        <v>0.02521573582771946</v>
+        <v>0.04602233757161359</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7425816669128837</v>
+        <v>0.352540310813392</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0226289966124321</v>
+        <v>0.03715017862020168</v>
       </c>
       <c r="V16" t="n">
-        <v>0.8168901353561694</v>
+        <v>0.3376487727398011</v>
       </c>
       <c r="W16" t="n">
-        <v>0.0142346735725995</v>
+        <v>0.03098537518318151</v>
       </c>
       <c r="X16" t="n">
-        <v>0.7204999999999999</v>
+        <v>0.3875</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.02521573582771946</v>
+        <v>0.04602233757161359</v>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>0.7205 ± 0.0252</t>
+          <t>0.3875 ± 0.0460</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.7426 ± 0.0226</t>
+          <t>0.3525 ± 0.0372</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>0.8169 ± 0.0142</t>
+          <t>0.3376 ± 0.0310</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>0.7205 ± 0.0252</t>
+          <t>0.3875 ± 0.0460</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>0.7205 ± 0.0252</t>
+          <t>0.3875 ± 0.0460</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>0.7426 ± 0.0226</t>
+          <t>0.3525 ± 0.0372</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>0.8169 ± 0.0142</t>
+          <t>0.3376 ± 0.0310</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>0.7205 ± 0.0252</t>
+          <t>0.3875 ± 0.0460</t>
         </is>
       </c>
       <c r="AH16" t="n">
-        <v>0.1075</v>
+        <v>0.09999999999999998</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.0678212270318308</v>
+        <v>0.1112073210872455</v>
       </c>
       <c r="AJ16" t="n">
-        <v>-0.002270848470252829</v>
+        <v>0.1247851354413896</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.1075</v>
+        <v>0.09999999999999998</v>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
@@ -3718,148 +3718,148 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ExtraTrees</t>
+          <t>NaiveBayes</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8240000000000001</v>
+        <v>0.485</v>
       </c>
       <c r="C17" t="n">
-        <v>0.02469817807045691</v>
+        <v>0.05797509043642027</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8177052906725901</v>
+        <v>0.3884614332892806</v>
       </c>
       <c r="E17" t="n">
-        <v>0.02578592983226878</v>
+        <v>0.04926617125562362</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8164120745306315</v>
+        <v>0.3748825660014655</v>
       </c>
       <c r="G17" t="n">
-        <v>0.02647286138062653</v>
+        <v>0.103253106459303</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8240000000000001</v>
+        <v>0.485</v>
       </c>
       <c r="I17" t="n">
-        <v>0.02469817807045691</v>
+        <v>0.05797509043642027</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.8240 ± 0.0247</t>
+          <t>0.4850 ± 0.0580</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.8177 ± 0.0258</t>
+          <t>0.3885 ± 0.0493</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.8164 ± 0.0265</t>
+          <t>0.3749 ± 0.1033</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0.8240 ± 0.0247</t>
+          <t>0.4850 ± 0.0580</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.8240 ± 0.0247</t>
+          <t>0.4850 ± 0.0580</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.8177 ± 0.0258</t>
+          <t>0.3885 ± 0.0493</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0.8164 ± 0.0265</t>
+          <t>0.3749 ± 0.1033</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>0.8240 ± 0.0247</t>
+          <t>0.4850 ± 0.0580</t>
         </is>
       </c>
       <c r="R17" t="n">
-        <v>0.7175</v>
+        <v>0.4525</v>
       </c>
       <c r="S17" t="n">
-        <v>0.02359967043084385</v>
+        <v>0.03987828704668466</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7398815798072279</v>
+        <v>0.3424611813376494</v>
       </c>
       <c r="U17" t="n">
-        <v>0.02149208500894103</v>
+        <v>0.02934375406805491</v>
       </c>
       <c r="V17" t="n">
-        <v>0.8160294753040294</v>
+        <v>0.2819780181439633</v>
       </c>
       <c r="W17" t="n">
-        <v>0.02063605637657615</v>
+        <v>0.03061914893120251</v>
       </c>
       <c r="X17" t="n">
-        <v>0.7175</v>
+        <v>0.4525</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.02359967043084385</v>
+        <v>0.03987828704668466</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>0.7175 ± 0.0236</t>
+          <t>0.4525 ± 0.0399</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.7399 ± 0.0215</t>
+          <t>0.3425 ± 0.0293</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>0.8160 ± 0.0206</t>
+          <t>0.2820 ± 0.0306</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>0.7175 ± 0.0236</t>
+          <t>0.4525 ± 0.0399</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>0.7175 ± 0.0236</t>
+          <t>0.4525 ± 0.0399</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>0.7399 ± 0.0215</t>
+          <t>0.3425 ± 0.0293</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>0.8160 ± 0.0206</t>
+          <t>0.2820 ± 0.0306</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>0.7175 ± 0.0236</t>
+          <t>0.4525 ± 0.0399</t>
         </is>
       </c>
       <c r="AH17" t="n">
-        <v>0.1065</v>
+        <v>0.03250000000000008</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.07782371086536222</v>
+        <v>0.04600025195163115</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.0003825992266021094</v>
+        <v>0.09290454785750213</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.1065</v>
+        <v>0.03250000000000008</v>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
@@ -3870,148 +3870,148 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NaiveBayes</t>
+          <t>ExtraTrees</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8090000000000002</v>
+        <v>0.4774999999999999</v>
       </c>
       <c r="C18" t="n">
-        <v>0.02579836342785244</v>
+        <v>0.06503204338375557</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7856952309335539</v>
+        <v>0.4691265033149707</v>
       </c>
       <c r="E18" t="n">
-        <v>0.02992064254649245</v>
+        <v>0.06795290437956898</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7897580695297388</v>
+        <v>0.4692555641821946</v>
       </c>
       <c r="G18" t="n">
-        <v>0.03856477005414511</v>
+        <v>0.07472771724947783</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8090000000000002</v>
+        <v>0.4774999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>0.02579836342785244</v>
+        <v>0.06503204338375557</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.8090 ± 0.0258</t>
+          <t>0.4775 ± 0.0650</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0.7857 ± 0.0299</t>
+          <t>0.4691 ± 0.0680</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0.7898 ± 0.0386</t>
+          <t>0.4693 ± 0.0747</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>0.8090 ± 0.0258</t>
+          <t>0.4775 ± 0.0650</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0.8090 ± 0.0258</t>
+          <t>0.4775 ± 0.0650</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>0.7857 ± 0.0299</t>
+          <t>0.4691 ± 0.0680</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>0.7898 ± 0.0386</t>
+          <t>0.4693 ± 0.0747</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>0.8090 ± 0.0258</t>
+          <t>0.4775 ± 0.0650</t>
         </is>
       </c>
       <c r="R18" t="n">
-        <v>0.7725000000000002</v>
+        <v>0.37</v>
       </c>
       <c r="S18" t="n">
-        <v>0.02821051813301795</v>
+        <v>0.05627314338711378</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7665686732006363</v>
+        <v>0.3362847653287579</v>
       </c>
       <c r="U18" t="n">
-        <v>0.02814661533497105</v>
+        <v>0.0482375805332325</v>
       </c>
       <c r="V18" t="n">
-        <v>0.7632603404979916</v>
+        <v>0.3247934755900835</v>
       </c>
       <c r="W18" t="n">
-        <v>0.02924767136212271</v>
+        <v>0.03788690753218912</v>
       </c>
       <c r="X18" t="n">
-        <v>0.7725000000000002</v>
+        <v>0.37</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.02821051813301795</v>
+        <v>0.05627314338711378</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>0.7725 ± 0.0282</t>
+          <t>0.3700 ± 0.0563</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.7666 ± 0.0281</t>
+          <t>0.3363 ± 0.0482</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>0.7633 ± 0.0292</t>
+          <t>0.3248 ± 0.0379</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>0.7725 ± 0.0282</t>
+          <t>0.3700 ± 0.0563</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>0.7725 ± 0.0282</t>
+          <t>0.3700 ± 0.0563</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>0.7666 ± 0.0281</t>
+          <t>0.3363 ± 0.0482</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>0.7633 ± 0.0292</t>
+          <t>0.3248 ± 0.0379</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>0.7725 ± 0.0282</t>
+          <t>0.3700 ± 0.0563</t>
         </is>
       </c>
       <c r="AH18" t="n">
-        <v>0.03649999999999998</v>
+        <v>0.1074999999999999</v>
       </c>
       <c r="AI18" t="n">
-        <v>0.0191265577329176</v>
+        <v>0.1328417379862128</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.02649772903174719</v>
+        <v>0.1444620885921111</v>
       </c>
       <c r="AK18" t="n">
-        <v>0.03649999999999998</v>
+        <v>0.1074999999999999</v>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
@@ -4022,148 +4022,148 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MLP</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8074999999999999</v>
+        <v>0.4699999999999999</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02552232138518923</v>
+        <v>0.07799572637865058</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8069554910760722</v>
+        <v>0.4464738356606046</v>
       </c>
       <c r="E19" t="n">
-        <v>0.02380568201797918</v>
+        <v>0.07281623112317112</v>
       </c>
       <c r="F19" t="n">
-        <v>0.808348378171001</v>
+        <v>0.4380473084886128</v>
       </c>
       <c r="G19" t="n">
-        <v>0.02217982684553994</v>
+        <v>0.08049181275833353</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8074999999999999</v>
+        <v>0.4699999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>0.02552232138518923</v>
+        <v>0.07799572637865058</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.8075 ± 0.0255</t>
+          <t>0.4700 ± 0.0780</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.8070 ± 0.0238</t>
+          <t>0.4465 ± 0.0728</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.8083 ± 0.0222</t>
+          <t>0.4380 ± 0.0805</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0.8075 ± 0.0255</t>
+          <t>0.4700 ± 0.0780</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0.8075 ± 0.0255</t>
+          <t>0.4700 ± 0.0780</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0.8070 ± 0.0238</t>
+          <t>0.4465 ± 0.0728</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0.8083 ± 0.0222</t>
+          <t>0.4380 ± 0.0805</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>0.8075 ± 0.0255</t>
+          <t>0.4700 ± 0.0780</t>
         </is>
       </c>
       <c r="R19" t="n">
-        <v>0.7040000000000001</v>
+        <v>0.3625</v>
       </c>
       <c r="S19" t="n">
-        <v>0.03680277767294805</v>
+        <v>0.05432668671002207</v>
       </c>
       <c r="T19" t="n">
-        <v>0.7272345527266039</v>
+        <v>0.323682382109807</v>
       </c>
       <c r="U19" t="n">
-        <v>0.03311353328519049</v>
+        <v>0.04715637281918291</v>
       </c>
       <c r="V19" t="n">
-        <v>0.8053433697361732</v>
+        <v>0.3125416400433184</v>
       </c>
       <c r="W19" t="n">
-        <v>0.01971851560894098</v>
+        <v>0.04310884461312551</v>
       </c>
       <c r="X19" t="n">
-        <v>0.7040000000000001</v>
+        <v>0.3625</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.03680277767294805</v>
+        <v>0.05432668671002207</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>0.7040 ± 0.0368</t>
+          <t>0.3625 ± 0.0543</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.7272 ± 0.0331</t>
+          <t>0.3237 ± 0.0472</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>0.8053 ± 0.0197</t>
+          <t>0.3125 ± 0.0431</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>0.7040 ± 0.0368</t>
+          <t>0.3625 ± 0.0543</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>0.7040 ± 0.0368</t>
+          <t>0.3625 ± 0.0543</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>0.7272 ± 0.0331</t>
+          <t>0.3237 ± 0.0472</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>0.8053 ± 0.0197</t>
+          <t>0.3125 ± 0.0431</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>0.7040 ± 0.0368</t>
+          <t>0.3625 ± 0.0543</t>
         </is>
       </c>
       <c r="AH19" t="n">
-        <v>0.1034999999999998</v>
+        <v>0.1074999999999999</v>
       </c>
       <c r="AI19" t="n">
-        <v>0.07972093834946836</v>
+        <v>0.1227914535507976</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.003005008434827872</v>
+        <v>0.1255056684452944</v>
       </c>
       <c r="AK19" t="n">
-        <v>0.1034999999999998</v>
+        <v>0.1074999999999999</v>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
@@ -4174,148 +4174,148 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>MLP</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8069999999999998</v>
+        <v>0.4275</v>
       </c>
       <c r="C20" t="n">
-        <v>0.02250925735484548</v>
+        <v>0.05945352993912324</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8008786340418022</v>
+        <v>0.420859292671839</v>
       </c>
       <c r="E20" t="n">
-        <v>0.02509907434611157</v>
+        <v>0.0582664427371178</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7978462200616508</v>
+        <v>0.4272267905705405</v>
       </c>
       <c r="G20" t="n">
-        <v>0.02661462081347623</v>
+        <v>0.06077100676915963</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8069999999999998</v>
+        <v>0.4275</v>
       </c>
       <c r="I20" t="n">
-        <v>0.02250925735484548</v>
+        <v>0.05945352993912324</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.8070 ± 0.0225</t>
+          <t>0.4275 ± 0.0595</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.8009 ± 0.0251</t>
+          <t>0.4209 ± 0.0583</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.7978 ± 0.0266</t>
+          <t>0.4272 ± 0.0608</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.8070 ± 0.0225</t>
+          <t>0.4275 ± 0.0595</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.8070 ± 0.0225</t>
+          <t>0.4275 ± 0.0595</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.8009 ± 0.0251</t>
+          <t>0.4209 ± 0.0583</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.7978 ± 0.0266</t>
+          <t>0.4272 ± 0.0608</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.8070 ± 0.0225</t>
+          <t>0.4275 ± 0.0595</t>
         </is>
       </c>
       <c r="R20" t="n">
-        <v>0.6819999999999999</v>
+        <v>0.375</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0204396129556745</v>
+        <v>0.05270462766947298</v>
       </c>
       <c r="T20" t="n">
-        <v>0.7079182364756985</v>
+        <v>0.3417448998020196</v>
       </c>
       <c r="U20" t="n">
-        <v>0.01875433200562023</v>
+        <v>0.04423250905732919</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8002301847805896</v>
+        <v>0.3347121761089152</v>
       </c>
       <c r="W20" t="n">
-        <v>0.01929628218260107</v>
+        <v>0.04258883152100918</v>
       </c>
       <c r="X20" t="n">
-        <v>0.6819999999999999</v>
+        <v>0.375</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.0204396129556745</v>
+        <v>0.05270462766947298</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>0.6820 ± 0.0204</t>
+          <t>0.3750 ± 0.0527</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.7079 ± 0.0188</t>
+          <t>0.3417 ± 0.0442</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>0.8002 ± 0.0193</t>
+          <t>0.3347 ± 0.0426</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>0.6820 ± 0.0204</t>
+          <t>0.3750 ± 0.0527</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>0.6820 ± 0.0204</t>
+          <t>0.3750 ± 0.0527</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>0.7079 ± 0.0188</t>
+          <t>0.3417 ± 0.0442</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>0.8002 ± 0.0193</t>
+          <t>0.3347 ± 0.0426</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>0.6820 ± 0.0204</t>
+          <t>0.3750 ± 0.0527</t>
         </is>
       </c>
       <c r="AH20" t="n">
-        <v>0.1249999999999999</v>
+        <v>0.05250000000000005</v>
       </c>
       <c r="AI20" t="n">
-        <v>0.09296039756610364</v>
+        <v>0.07911439286981942</v>
       </c>
       <c r="AJ20" t="n">
-        <v>-0.002383964718938758</v>
+        <v>0.09251461446162529</v>
       </c>
       <c r="AK20" t="n">
-        <v>0.1249999999999999</v>
+        <v>0.05250000000000005</v>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
@@ -4330,144 +4330,144 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.784</v>
+        <v>0.4175</v>
       </c>
       <c r="C21" t="n">
-        <v>0.02913569784454954</v>
+        <v>0.0601502747753953</v>
       </c>
       <c r="D21" t="n">
-        <v>0.785293092246484</v>
+        <v>0.4187416830432881</v>
       </c>
       <c r="E21" t="n">
-        <v>0.02860525768452616</v>
+        <v>0.05976891793014379</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7880825733490411</v>
+        <v>0.4405900453712953</v>
       </c>
       <c r="G21" t="n">
-        <v>0.02887004930408354</v>
+        <v>0.06784141632447085</v>
       </c>
       <c r="H21" t="n">
-        <v>0.784</v>
+        <v>0.4175</v>
       </c>
       <c r="I21" t="n">
-        <v>0.02913569784454954</v>
+        <v>0.0601502747753953</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.7840 ± 0.0291</t>
+          <t>0.4175 ± 0.0602</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.7853 ± 0.0286</t>
+          <t>0.4187 ± 0.0598</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.7881 ± 0.0289</t>
+          <t>0.4406 ± 0.0678</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.7840 ± 0.0291</t>
+          <t>0.4175 ± 0.0602</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.7840 ± 0.0291</t>
+          <t>0.4175 ± 0.0602</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.7853 ± 0.0286</t>
+          <t>0.4187 ± 0.0598</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.7881 ± 0.0289</t>
+          <t>0.4406 ± 0.0678</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.7840 ± 0.0291</t>
+          <t>0.4175 ± 0.0602</t>
         </is>
       </c>
       <c r="R21" t="n">
-        <v>0.6325</v>
+        <v>0.3875000000000001</v>
       </c>
       <c r="S21" t="n">
-        <v>0.04104536785341586</v>
+        <v>0.06263873490988711</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6618426726971874</v>
+        <v>0.3441634354530214</v>
       </c>
       <c r="U21" t="n">
-        <v>0.03707232762900146</v>
+        <v>0.05281902859808141</v>
       </c>
       <c r="V21" t="n">
-        <v>0.7511015945240864</v>
+        <v>0.327384385984635</v>
       </c>
       <c r="W21" t="n">
-        <v>0.02425709812870806</v>
+        <v>0.04551896719438788</v>
       </c>
       <c r="X21" t="n">
-        <v>0.6325000000000001</v>
+        <v>0.3875000000000001</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.04104536785341584</v>
+        <v>0.06263873490988711</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.6325 ± 0.0410</t>
+          <t>0.3875 ± 0.0626</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.6618 ± 0.0371</t>
+          <t>0.3442 ± 0.0528</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.7511 ± 0.0243</t>
+          <t>0.3274 ± 0.0455</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>0.6325 ± 0.0410</t>
+          <t>0.3875 ± 0.0626</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>0.6325 ± 0.0410</t>
+          <t>0.3875 ± 0.0626</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>0.6618 ± 0.0371</t>
+          <t>0.3442 ± 0.0528</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>0.7511 ± 0.0243</t>
+          <t>0.3274 ± 0.0455</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>0.6325 ± 0.0410</t>
+          <t>0.3875 ± 0.0626</t>
         </is>
       </c>
       <c r="AH21" t="n">
-        <v>0.1515000000000001</v>
+        <v>0.02999999999999992</v>
       </c>
       <c r="AI21" t="n">
-        <v>0.1234504195492966</v>
+        <v>0.07457824759026677</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.03698097882495466</v>
+        <v>0.1132056593866603</v>
       </c>
       <c r="AK21" t="n">
-        <v>0.1515</v>
+        <v>0.02999999999999992</v>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
@@ -4523,16 +4523,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1004</v>
+        <v>0.10125</v>
       </c>
       <c r="C2" t="n">
-        <v>0.07076871099479824</v>
+        <v>0.09573847343171399</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007103183447347972</v>
+        <v>0.09744358810078431</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1004</v>
+        <v>0.10125</v>
       </c>
     </row>
     <row r="3">
@@ -4542,16 +4542,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.35535</v>
+        <v>0.17325</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3715135721959001</v>
+        <v>0.2226780277443293</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1981491026935139</v>
+        <v>0.209112509901966</v>
       </c>
       <c r="E3" t="n">
-        <v>0.35535</v>
+        <v>0.17325</v>
       </c>
     </row>
   </sheetData>
@@ -4763,148 +4763,148 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>GradientBoost</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8385000000000001</v>
+        <v>0.525</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02582526755804176</v>
+        <v>0.05270462766947299</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8305541949820711</v>
+        <v>0.4933690349824439</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02852270307867011</v>
+        <v>0.05378629795968384</v>
       </c>
       <c r="F2" t="n">
-        <v>0.829281699641512</v>
+        <v>0.4829841867174139</v>
       </c>
       <c r="G2" t="n">
-        <v>0.02975094206425076</v>
+        <v>0.06111253566375451</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8385000000000001</v>
+        <v>0.525</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02582526755804176</v>
+        <v>0.05270462766947299</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.8385 ± 0.0258</t>
+          <t>0.5250 ± 0.0527</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.8306 ± 0.0285</t>
+          <t>0.4934 ± 0.0538</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.8293 ± 0.0298</t>
+          <t>0.4830 ± 0.0611</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.8385 ± 0.0258</t>
+          <t>0.5250 ± 0.0527</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.8385 ± 0.0258</t>
+          <t>0.5250 ± 0.0527</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.8306 ± 0.0285</t>
+          <t>0.4934 ± 0.0538</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.8293 ± 0.0298</t>
+          <t>0.4830 ± 0.0611</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0.8385 ± 0.0258</t>
+          <t>0.5250 ± 0.0527</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>0.5125</v>
+        <v>0.3875</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1123795651649652</v>
+        <v>0.08599903100229286</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5395203310251679</v>
+        <v>0.3025445867729023</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1034656199890816</v>
+        <v>0.06458889472210863</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6429581736983061</v>
+        <v>0.2871417705278</v>
       </c>
       <c r="W2" t="n">
-        <v>0.04306004027927952</v>
+        <v>0.0545974671428285</v>
       </c>
       <c r="X2" t="n">
-        <v>0.5125</v>
+        <v>0.3875</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1123795651649652</v>
+        <v>0.08599903100229286</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.5125 ± 0.1124</t>
+          <t>0.3875 ± 0.0860</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.5395 ± 0.1035</t>
+          <t>0.3025 ± 0.0646</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.6430 ± 0.0431</t>
+          <t>0.2871 ± 0.0546</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0.5125 ± 0.1124</t>
+          <t>0.3875 ± 0.0860</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0.5125 ± 0.1124</t>
+          <t>0.3875 ± 0.0860</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>0.5395 ± 0.1035</t>
+          <t>0.3025 ± 0.0646</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.6430 ± 0.0431</t>
+          <t>0.2871 ± 0.0546</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.5125 ± 0.1124</t>
+          <t>0.3875 ± 0.0860</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>0.3260000000000002</v>
+        <v>0.1375000000000001</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.2910338639569031</v>
+        <v>0.1908244482095416</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.1863235259432059</v>
+        <v>0.1958424161896139</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.3260000000000002</v>
+        <v>0.1375000000000001</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -4915,148 +4915,148 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AdaBoost</t>
+          <t>SVM-RBF</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.837</v>
+        <v>0.515</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02335713072180646</v>
+        <v>0.04594682917363409</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8271380947617498</v>
+        <v>0.4010974358974359</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02698482468705257</v>
+        <v>0.05121627639470829</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8274717782384444</v>
+        <v>0.344789166784749</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02800542328232125</v>
+        <v>0.06757227328844036</v>
       </c>
       <c r="H3" t="n">
-        <v>0.837</v>
+        <v>0.515</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02335713072180646</v>
+        <v>0.04594682917363409</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.8370 ± 0.0234</t>
+          <t>0.5150 ± 0.0459</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.8271 ± 0.0270</t>
+          <t>0.4011 ± 0.0512</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.8275 ± 0.0280</t>
+          <t>0.3448 ± 0.0676</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.8370 ± 0.0234</t>
+          <t>0.5150 ± 0.0459</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.8370 ± 0.0234</t>
+          <t>0.5150 ± 0.0459</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.8271 ± 0.0270</t>
+          <t>0.4011 ± 0.0512</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.8275 ± 0.0280</t>
+          <t>0.3448 ± 0.0676</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>0.8370 ± 0.0234</t>
+          <t>0.5150 ± 0.0459</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>0.5305000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1057368326449104</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5488756106178502</v>
+        <v>0.1</v>
       </c>
       <c r="U3" t="n">
-        <v>0.07559652370376714</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6271948053271059</v>
+        <v>0.0625</v>
       </c>
       <c r="W3" t="n">
-        <v>0.05744903576928705</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.5305000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1057368326449104</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.5305 ± 0.1057</t>
+          <t>0.2500 ± 0.0000</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.5489 ± 0.0756</t>
+          <t>0.1000 ± 0.0000</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.6272 ± 0.0574</t>
+          <t>0.0625 ± 0.0000</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>0.5305 ± 0.1057</t>
+          <t>0.2500 ± 0.0000</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0.5305 ± 0.1057</t>
+          <t>0.2500 ± 0.0000</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>0.5489 ± 0.0756</t>
+          <t>0.1000 ± 0.0000</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.6272 ± 0.0574</t>
+          <t>0.0625 ± 0.0000</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.5305 ± 0.1057</t>
+          <t>0.2500 ± 0.0000</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>0.3064999999999999</v>
+        <v>0.265</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.2782624841438996</v>
+        <v>0.3010974358974359</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.2002769729113385</v>
+        <v>0.282289166784749</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.3064999999999999</v>
+        <v>0.265</v>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
@@ -5067,148 +5067,148 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SVM-RBF</t>
+          <t>AdaBoost</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8334999999999999</v>
+        <v>0.515</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01826502425706331</v>
+        <v>0.04887626099538394</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8099526079303931</v>
+        <v>0.4459274392015852</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02569511545306504</v>
+        <v>0.04904546419911374</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8244128167802897</v>
+        <v>0.4204506553904218</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02264298462168463</v>
+        <v>0.07436424082867353</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8334999999999999</v>
+        <v>0.515</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01826502425706331</v>
+        <v>0.04887626099538394</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.8335 ± 0.0183</t>
+          <t>0.5150 ± 0.0489</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.8100 ± 0.0257</t>
+          <t>0.4459 ± 0.0490</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.8244 ± 0.0226</t>
+          <t>0.4205 ± 0.0744</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.8335 ± 0.0183</t>
+          <t>0.5150 ± 0.0489</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.8335 ± 0.0183</t>
+          <t>0.5150 ± 0.0489</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.8100 ± 0.0257</t>
+          <t>0.4459 ± 0.0490</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.8244 ± 0.0226</t>
+          <t>0.4205 ± 0.0744</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.8335 ± 0.0183</t>
+          <t>0.5150 ± 0.0489</t>
         </is>
       </c>
       <c r="R4" t="n">
-        <v>0.2305</v>
+        <v>0.26</v>
       </c>
       <c r="S4" t="n">
-        <v>0.008316649966583095</v>
+        <v>0.04116363011742822</v>
       </c>
       <c r="T4" t="n">
-        <v>0.09727722370394457</v>
+        <v>0.1614814135140222</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01464171707055061</v>
+        <v>0.06196347794844405</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5673248815657512</v>
+        <v>0.2553684824807116</v>
       </c>
       <c r="W4" t="n">
-        <v>0.3168651752883881</v>
+        <v>0.1394080724034463</v>
       </c>
       <c r="X4" t="n">
-        <v>0.2305</v>
+        <v>0.26</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.008316649966583095</v>
+        <v>0.04116363011742822</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.2305 ± 0.0083</t>
+          <t>0.2600 ± 0.0412</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.0973 ± 0.0146</t>
+          <t>0.1615 ± 0.0620</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.5673 ± 0.3169</t>
+          <t>0.2554 ± 0.1394</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.2305 ± 0.0083</t>
+          <t>0.2600 ± 0.0412</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0.2305 ± 0.0083</t>
+          <t>0.2600 ± 0.0412</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>0.0973 ± 0.0146</t>
+          <t>0.1615 ± 0.0620</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.5673 ± 0.3169</t>
+          <t>0.2554 ± 0.1394</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.2305 ± 0.0083</t>
+          <t>0.2600 ± 0.0412</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>0.6029999999999999</v>
+        <v>0.255</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.7126753842264486</v>
+        <v>0.2844460256875629</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.2570879352145384</v>
+        <v>0.1650821729097102</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.6029999999999999</v>
+        <v>0.255</v>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
@@ -5219,148 +5219,148 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GradientBoost</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.833</v>
+        <v>0.5049999999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0240601099101581</v>
+        <v>0.0483045891539648</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8246020797017092</v>
+        <v>0.3946722798843776</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02529261929811836</v>
+        <v>0.05058216691498373</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8239151747889606</v>
+        <v>0.3328350963552577</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02640491712024394</v>
+        <v>0.05354862018695906</v>
       </c>
       <c r="H5" t="n">
-        <v>0.833</v>
+        <v>0.5049999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0240601099101581</v>
+        <v>0.0483045891539648</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.8330 ± 0.0241</t>
+          <t>0.5050 ± 0.0483</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.8246 ± 0.0253</t>
+          <t>0.3947 ± 0.0506</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.8239 ± 0.0264</t>
+          <t>0.3328 ± 0.0535</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.8330 ± 0.0241</t>
+          <t>0.5050 ± 0.0483</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.8330 ± 0.0241</t>
+          <t>0.5050 ± 0.0483</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.8246 ± 0.0253</t>
+          <t>0.3947 ± 0.0506</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.8239 ± 0.0264</t>
+          <t>0.3328 ± 0.0535</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.8330 ± 0.0241</t>
+          <t>0.5050 ± 0.0483</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>0.3895</v>
+        <v>0.25</v>
       </c>
       <c r="S5" t="n">
-        <v>0.106860500965823</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4091344775251774</v>
+        <v>0.1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1220295067774568</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6031499807370405</v>
+        <v>0.0625</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1038495103829512</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3895</v>
+        <v>0.25</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.106860500965823</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.3895 ± 0.1069</t>
+          <t>0.2500 ± 0.0000</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.4091 ± 0.1220</t>
+          <t>0.1000 ± 0.0000</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.6031 ± 0.1038</t>
+          <t>0.0625 ± 0.0000</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.3895 ± 0.1069</t>
+          <t>0.2500 ± 0.0000</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0.3895 ± 0.1069</t>
+          <t>0.2500 ± 0.0000</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0.4091 ± 0.1220</t>
+          <t>0.1000 ± 0.0000</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.6031 ± 0.1038</t>
+          <t>0.0625 ± 0.0000</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.3895 ± 0.1069</t>
+          <t>0.2500 ± 0.0000</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>0.4435</v>
+        <v>0.2549999999999999</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.4154676021765318</v>
+        <v>0.2946722798843776</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.2207651940519201</v>
+        <v>0.2703350963552577</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.4435</v>
+        <v>0.2549999999999999</v>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
@@ -5371,148 +5371,148 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.828</v>
+        <v>0.4875</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02175622516277427</v>
+        <v>0.06373774391990981</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8104028939447145</v>
+        <v>0.4637476319006376</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02627109794847402</v>
+        <v>0.06802787926675574</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8146192868859166</v>
+        <v>0.4624339081811907</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02793976606486409</v>
+        <v>0.07612364353088311</v>
       </c>
       <c r="H6" t="n">
-        <v>0.828</v>
+        <v>0.4875</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02175622516277427</v>
+        <v>0.06373774391990981</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.8280 ± 0.0218</t>
+          <t>0.4875 ± 0.0637</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.8104 ± 0.0263</t>
+          <t>0.4637 ± 0.0680</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.8146 ± 0.0279</t>
+          <t>0.4624 ± 0.0761</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>0.8280 ± 0.0218</t>
+          <t>0.4875 ± 0.0637</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.8280 ± 0.0218</t>
+          <t>0.4875 ± 0.0637</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.8104 ± 0.0263</t>
+          <t>0.4637 ± 0.0680</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.8146 ± 0.0279</t>
+          <t>0.4624 ± 0.0761</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>0.8280 ± 0.0218</t>
+          <t>0.4875 ± 0.0637</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>0.2305</v>
+        <v>0.33</v>
       </c>
       <c r="S6" t="n">
-        <v>0.008316649966583095</v>
+        <v>0.0779957263786506</v>
       </c>
       <c r="T6" t="n">
-        <v>0.09727722370394457</v>
+        <v>0.2723531325719486</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01464171707055061</v>
+        <v>0.07142745007587166</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5673248815657512</v>
+        <v>0.2840750565457549</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3168651752883881</v>
+        <v>0.05686880834870454</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2305</v>
+        <v>0.33</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.008316649966583095</v>
+        <v>0.0779957263786506</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.2305 ± 0.0083</t>
+          <t>0.3300 ± 0.0780</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.0973 ± 0.0146</t>
+          <t>0.2724 ± 0.0714</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.5673 ± 0.3169</t>
+          <t>0.2841 ± 0.0569</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>0.2305 ± 0.0083</t>
+          <t>0.3300 ± 0.0780</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0.2305 ± 0.0083</t>
+          <t>0.3300 ± 0.0780</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>0.0973 ± 0.0146</t>
+          <t>0.2724 ± 0.0714</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.5673 ± 0.3169</t>
+          <t>0.2841 ± 0.0569</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>0.2305 ± 0.0083</t>
+          <t>0.3300 ± 0.0780</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>0.5974999999999999</v>
+        <v>0.1575</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.71312567024077</v>
+        <v>0.191394499328689</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.2472944053201653</v>
+        <v>0.1783588516354359</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.5974999999999999</v>
+        <v>0.1575</v>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
@@ -5523,148 +5523,148 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ExtraTrees</t>
+          <t>NaiveBayes</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8240000000000001</v>
+        <v>0.485</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02469817807045691</v>
+        <v>0.05797509043642027</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8177052906725901</v>
+        <v>0.3884614332892806</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02578592983226878</v>
+        <v>0.04926617125562362</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8164120745306315</v>
+        <v>0.3748825660014655</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02647286138062653</v>
+        <v>0.103253106459303</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8240000000000001</v>
+        <v>0.485</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02469817807045691</v>
+        <v>0.05797509043642027</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.8240 ± 0.0247</t>
+          <t>0.4850 ± 0.0580</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.8177 ± 0.0258</t>
+          <t>0.3885 ± 0.0493</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.8164 ± 0.0265</t>
+          <t>0.3749 ± 0.1033</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.8240 ± 0.0247</t>
+          <t>0.4850 ± 0.0580</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.8240 ± 0.0247</t>
+          <t>0.4850 ± 0.0580</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.8177 ± 0.0258</t>
+          <t>0.3885 ± 0.0493</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.8164 ± 0.0265</t>
+          <t>0.3749 ± 0.1033</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.8240 ± 0.0247</t>
+          <t>0.4850 ± 0.0580</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>0.5954999999999999</v>
+        <v>0.295</v>
       </c>
       <c r="S7" t="n">
-        <v>0.08725600902580355</v>
+        <v>0.07340905181848413</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6039978948807547</v>
+        <v>0.1753634781546781</v>
       </c>
       <c r="U7" t="n">
-        <v>0.05700630742689323</v>
+        <v>0.105704321437552</v>
       </c>
       <c r="V7" t="n">
-        <v>0.636558589265263</v>
+        <v>0.1773573523250943</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01581256914988814</v>
+        <v>0.1488571142648826</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5954999999999999</v>
+        <v>0.295</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.08725600902580355</v>
+        <v>0.07340905181848413</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.5955 ± 0.0873</t>
+          <t>0.2950 ± 0.0734</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.6040 ± 0.0570</t>
+          <t>0.1754 ± 0.1057</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.6366 ± 0.0158</t>
+          <t>0.1774 ± 0.1489</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>0.5955 ± 0.0873</t>
+          <t>0.2950 ± 0.0734</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0.5955 ± 0.0873</t>
+          <t>0.2950 ± 0.0734</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>0.6040 ± 0.0570</t>
+          <t>0.1754 ± 0.1057</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.6366 ± 0.0158</t>
+          <t>0.1774 ± 0.1489</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>0.5955 ± 0.0873</t>
+          <t>0.2950 ± 0.0734</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>0.2285000000000001</v>
+        <v>0.19</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.2137073957918354</v>
+        <v>0.2130979551346024</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.1798534852653685</v>
+        <v>0.1975252136763712</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.2285000000000001</v>
+        <v>0.19</v>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
@@ -5675,148 +5675,148 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NaiveBayes</t>
+          <t>ExtraTrees</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8090000000000002</v>
+        <v>0.4774999999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02579836342785244</v>
+        <v>0.06503204338375557</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7856952309335539</v>
+        <v>0.4691265033149707</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02992064254649245</v>
+        <v>0.06795290437956898</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7897580695297388</v>
+        <v>0.4692555641821946</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03856477005414511</v>
+        <v>0.07472771724947783</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8090000000000002</v>
+        <v>0.4774999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02579836342785244</v>
+        <v>0.06503204338375557</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.8090 ± 0.0258</t>
+          <t>0.4775 ± 0.0650</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.7857 ± 0.0299</t>
+          <t>0.4691 ± 0.0680</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.7898 ± 0.0386</t>
+          <t>0.4693 ± 0.0747</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.8090 ± 0.0258</t>
+          <t>0.4775 ± 0.0650</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.8090 ± 0.0258</t>
+          <t>0.4775 ± 0.0650</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.7857 ± 0.0299</t>
+          <t>0.4691 ± 0.0680</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.7898 ± 0.0386</t>
+          <t>0.4693 ± 0.0747</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.8090 ± 0.0258</t>
+          <t>0.4775 ± 0.0650</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>0.5655</v>
+        <v>0.3225</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1774268237267911</v>
+        <v>0.08032053840014326</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5443376427995192</v>
+        <v>0.2645316244756154</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1772402845995828</v>
+        <v>0.08099575491445819</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6655303303483318</v>
+        <v>0.2869117454018014</v>
       </c>
       <c r="W8" t="n">
-        <v>0.09270492416950747</v>
+        <v>0.08004562326683869</v>
       </c>
       <c r="X8" t="n">
-        <v>0.5655</v>
+        <v>0.3225</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.1774268237267911</v>
+        <v>0.08032053840014326</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.5655 ± 0.1774</t>
+          <t>0.3225 ± 0.0803</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.5443 ± 0.1772</t>
+          <t>0.2645 ± 0.0810</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.6655 ± 0.0927</t>
+          <t>0.2869 ± 0.0800</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>0.5655 ± 0.1774</t>
+          <t>0.3225 ± 0.0803</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0.5655 ± 0.1774</t>
+          <t>0.3225 ± 0.0803</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>0.5443 ± 0.1772</t>
+          <t>0.2645 ± 0.0810</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.6655 ± 0.0927</t>
+          <t>0.2869 ± 0.0800</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>0.5655 ± 0.1774</t>
+          <t>0.3225 ± 0.0803</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>0.2435000000000002</v>
+        <v>0.1549999999999999</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.2413575881340346</v>
+        <v>0.2045948788393553</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.1242277391814071</v>
+        <v>0.1823438187803932</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.2435000000000002</v>
+        <v>0.1549999999999999</v>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
@@ -5827,148 +5827,148 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MLP</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8074999999999999</v>
+        <v>0.4699999999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02552232138518923</v>
+        <v>0.07799572637865058</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8069554910760722</v>
+        <v>0.4464738356606046</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02380568201797918</v>
+        <v>0.07281623112317112</v>
       </c>
       <c r="F9" t="n">
-        <v>0.808348378171001</v>
+        <v>0.4380473084886128</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02217982684553994</v>
+        <v>0.08049181275833353</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8074999999999999</v>
+        <v>0.4699999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02552232138518923</v>
+        <v>0.07799572637865058</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.8075 ± 0.0255</t>
+          <t>0.4700 ± 0.0780</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.8070 ± 0.0238</t>
+          <t>0.4465 ± 0.0728</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.8083 ± 0.0222</t>
+          <t>0.4380 ± 0.0805</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.8075 ± 0.0255</t>
+          <t>0.4700 ± 0.0780</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.8075 ± 0.0255</t>
+          <t>0.4700 ± 0.0780</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.8070 ± 0.0238</t>
+          <t>0.4465 ± 0.0728</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.8083 ± 0.0222</t>
+          <t>0.4380 ± 0.0805</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.8075 ± 0.0255</t>
+          <t>0.4700 ± 0.0780</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>0.4575</v>
+        <v>0.3775000000000001</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2711933504592864</v>
+        <v>0.07587453093393358</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3571250032074406</v>
+        <v>0.3279301962087951</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2925635451498613</v>
+        <v>0.06211624669037222</v>
       </c>
       <c r="V9" t="n">
-        <v>0.4823265278645917</v>
+        <v>0.3122595904878523</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2529046991217041</v>
+        <v>0.05659514923852697</v>
       </c>
       <c r="X9" t="n">
-        <v>0.4575</v>
+        <v>0.3775000000000001</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.2711933504592864</v>
+        <v>0.07587453093393358</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.4575 ± 0.2712</t>
+          <t>0.3775 ± 0.0759</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.3571 ± 0.2926</t>
+          <t>0.3279 ± 0.0621</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.4823 ± 0.2529</t>
+          <t>0.3123 ± 0.0566</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0.4575 ± 0.2712</t>
+          <t>0.3775 ± 0.0759</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0.4575 ± 0.2712</t>
+          <t>0.3775 ± 0.0759</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>0.3571 ± 0.2926</t>
+          <t>0.3279 ± 0.0621</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.4823 ± 0.2529</t>
+          <t>0.3123 ± 0.0566</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>0.4575 ± 0.2712</t>
+          <t>0.3775 ± 0.0759</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>0.3499999999999999</v>
+        <v>0.09249999999999986</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.4498304878686316</v>
+        <v>0.1185436394518095</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.3260218503064093</v>
+        <v>0.1257877180007605</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.3499999999999999</v>
+        <v>0.09249999999999986</v>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
@@ -5979,148 +5979,148 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>MLP</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8069999999999998</v>
+        <v>0.4275</v>
       </c>
       <c r="C10" t="n">
-        <v>0.02250925735484548</v>
+        <v>0.05945352993912324</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8008786340418022</v>
+        <v>0.420859292671839</v>
       </c>
       <c r="E10" t="n">
-        <v>0.02509907434611157</v>
+        <v>0.0582664427371178</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7978462200616508</v>
+        <v>0.4272267905705405</v>
       </c>
       <c r="G10" t="n">
-        <v>0.02661462081347623</v>
+        <v>0.06077100676915963</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8069999999999998</v>
+        <v>0.4275</v>
       </c>
       <c r="I10" t="n">
-        <v>0.02250925735484548</v>
+        <v>0.05945352993912324</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.8070 ± 0.0225</t>
+          <t>0.4275 ± 0.0595</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.8009 ± 0.0251</t>
+          <t>0.4209 ± 0.0583</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.7978 ± 0.0266</t>
+          <t>0.4272 ± 0.0608</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.8070 ± 0.0225</t>
+          <t>0.4275 ± 0.0595</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.8070 ± 0.0225</t>
+          <t>0.4275 ± 0.0595</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.8009 ± 0.0251</t>
+          <t>0.4209 ± 0.0583</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.7978 ± 0.0266</t>
+          <t>0.4272 ± 0.0608</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.8070 ± 0.0225</t>
+          <t>0.4275 ± 0.0595</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>0.6029999999999999</v>
+        <v>0.295</v>
       </c>
       <c r="S10" t="n">
-        <v>0.06490163497341357</v>
+        <v>0.09486832980505137</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6279760268799872</v>
+        <v>0.1411864406779661</v>
       </c>
       <c r="U10" t="n">
-        <v>0.05528025871606659</v>
+        <v>0.0868286408385216</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6853656925276244</v>
+        <v>0.095125</v>
       </c>
       <c r="W10" t="n">
-        <v>0.02424663571614332</v>
+        <v>0.06877953910866226</v>
       </c>
       <c r="X10" t="n">
-        <v>0.6029999999999999</v>
+        <v>0.295</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.06490163497341357</v>
+        <v>0.09486832980505137</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.6030 ± 0.0649</t>
+          <t>0.2950 ± 0.0949</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.6280 ± 0.0553</t>
+          <t>0.1412 ± 0.0868</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.6854 ± 0.0242</t>
+          <t>0.0951 ± 0.0688</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>0.6030 ± 0.0649</t>
+          <t>0.2950 ± 0.0949</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0.6030 ± 0.0649</t>
+          <t>0.2950 ± 0.0949</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>0.6280 ± 0.0553</t>
+          <t>0.1412 ± 0.0868</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.6854 ± 0.0242</t>
+          <t>0.0951 ± 0.0688</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>0.6030 ± 0.0649</t>
+          <t>0.2950 ± 0.0949</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>0.204</v>
+        <v>0.1325</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.1729026071618149</v>
+        <v>0.2796728519938729</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.1124805275340265</v>
+        <v>0.3321017905705405</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.204</v>
+        <v>0.1325</v>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
@@ -6135,144 +6135,144 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.784</v>
+        <v>0.4175</v>
       </c>
       <c r="C11" t="n">
-        <v>0.02913569784454954</v>
+        <v>0.0601502747753953</v>
       </c>
       <c r="D11" t="n">
-        <v>0.785293092246484</v>
+        <v>0.4187416830432881</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02860525768452616</v>
+        <v>0.05976891793014379</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7880825733490411</v>
+        <v>0.4405900453712953</v>
       </c>
       <c r="G11" t="n">
-        <v>0.02887004930408354</v>
+        <v>0.06784141632447085</v>
       </c>
       <c r="H11" t="n">
-        <v>0.784</v>
+        <v>0.4175</v>
       </c>
       <c r="I11" t="n">
-        <v>0.02913569784454954</v>
+        <v>0.0601502747753953</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.7840 ± 0.0291</t>
+          <t>0.4175 ± 0.0602</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.7853 ± 0.0286</t>
+          <t>0.4187 ± 0.0598</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.7881 ± 0.0289</t>
+          <t>0.4406 ± 0.0678</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.7840 ± 0.0291</t>
+          <t>0.4175 ± 0.0602</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.7840 ± 0.0291</t>
+          <t>0.4175 ± 0.0602</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.7853 ± 0.0286</t>
+          <t>0.4187 ± 0.0598</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.7881 ± 0.0289</t>
+          <t>0.4406 ± 0.0678</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.7840 ± 0.0291</t>
+          <t>0.4175 ± 0.0602</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>0.533</v>
+        <v>0.325</v>
       </c>
       <c r="S11" t="n">
-        <v>0.08944893018427393</v>
+        <v>0.05651941652604389</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5585204539883526</v>
+        <v>0.2703054200272416</v>
       </c>
       <c r="U11" t="n">
-        <v>0.07763899105273228</v>
+        <v>0.0595591187161921</v>
       </c>
       <c r="V11" t="n">
-        <v>0.6609231821422814</v>
+        <v>0.2791311912544671</v>
       </c>
       <c r="W11" t="n">
-        <v>0.07338396495062781</v>
+        <v>0.06063250779160817</v>
       </c>
       <c r="X11" t="n">
-        <v>0.533</v>
+        <v>0.325</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.08944893018427393</v>
+        <v>0.05651941652604389</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.5330 ± 0.0894</t>
+          <t>0.3250 ± 0.0565</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.5585 ± 0.0776</t>
+          <t>0.2703 ± 0.0596</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.6609 ± 0.0734</t>
+          <t>0.2791 ± 0.0606</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>0.5330 ± 0.0894</t>
+          <t>0.3250 ± 0.0565</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0.5330 ± 0.0894</t>
+          <t>0.3250 ± 0.0565</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>0.5585 ± 0.0776</t>
+          <t>0.2703 ± 0.0596</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.6609 ± 0.0734</t>
+          <t>0.2791 ± 0.0606</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0.5330 ± 0.0894</t>
+          <t>0.3250 ± 0.0565</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>0.251</v>
+        <v>0.09249999999999997</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.2267726382581314</v>
+        <v>0.1484362630160465</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.1271593912067597</v>
+        <v>0.1614588541168283</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.251</v>
+        <v>0.09249999999999997</v>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
@@ -6489,148 +6489,148 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>GradientBoost</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8385000000000001</v>
+        <v>0.525</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02582526755804176</v>
+        <v>0.05270462766947299</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8305541949820711</v>
+        <v>0.4933690349824439</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02852270307867011</v>
+        <v>0.05378629795968384</v>
       </c>
       <c r="F2" t="n">
-        <v>0.829281699641512</v>
+        <v>0.4829841867174139</v>
       </c>
       <c r="G2" t="n">
-        <v>0.02975094206425076</v>
+        <v>0.06111253566375451</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8385000000000001</v>
+        <v>0.525</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02582526755804176</v>
+        <v>0.05270462766947299</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.8385 ± 0.0258</t>
+          <t>0.5250 ± 0.0527</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.8306 ± 0.0285</t>
+          <t>0.4934 ± 0.0538</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.8293 ± 0.0298</t>
+          <t>0.4830 ± 0.0611</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.8385 ± 0.0258</t>
+          <t>0.5250 ± 0.0527</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.8385 ± 0.0258</t>
+          <t>0.5250 ± 0.0527</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.8306 ± 0.0285</t>
+          <t>0.4934 ± 0.0538</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.8293 ± 0.0298</t>
+          <t>0.4830 ± 0.0611</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0.8385 ± 0.0258</t>
+          <t>0.5250 ± 0.0527</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>0.7464999999999999</v>
+        <v>0.415</v>
       </c>
       <c r="S2" t="n">
-        <v>0.02068950351157698</v>
+        <v>0.04594682917363407</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7644637239952305</v>
+        <v>0.3702766543942891</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01887158862533338</v>
+        <v>0.03913577841474109</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8155266283306348</v>
+        <v>0.3461739410138925</v>
       </c>
       <c r="W2" t="n">
-        <v>0.02103133590380068</v>
+        <v>0.04677190854226341</v>
       </c>
       <c r="X2" t="n">
-        <v>0.7464999999999999</v>
+        <v>0.415</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.02068950351157698</v>
+        <v>0.04594682917363407</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.7465 ± 0.0207</t>
+          <t>0.4150 ± 0.0459</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.7645 ± 0.0189</t>
+          <t>0.3703 ± 0.0391</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.8155 ± 0.0210</t>
+          <t>0.3462 ± 0.0468</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0.7465 ± 0.0207</t>
+          <t>0.4150 ± 0.0459</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0.7465 ± 0.0207</t>
+          <t>0.4150 ± 0.0459</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>0.7645 ± 0.0189</t>
+          <t>0.3703 ± 0.0391</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.8155 ± 0.0210</t>
+          <t>0.3462 ± 0.0468</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.7465 ± 0.0207</t>
+          <t>0.4150 ± 0.0459</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>0.09200000000000019</v>
+        <v>0.11</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.06609047098684051</v>
+        <v>0.1230923805881548</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.01375507131087716</v>
+        <v>0.1368102457035213</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.09200000000000019</v>
+        <v>0.11</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -6641,148 +6641,148 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AdaBoost</t>
+          <t>SVM-RBF</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.837</v>
+        <v>0.515</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02335713072180646</v>
+        <v>0.04594682917363409</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8271380947617498</v>
+        <v>0.4010974358974359</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02698482468705257</v>
+        <v>0.05121627639470829</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8274717782384444</v>
+        <v>0.344789166784749</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02800542328232125</v>
+        <v>0.06757227328844036</v>
       </c>
       <c r="H3" t="n">
-        <v>0.837</v>
+        <v>0.515</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02335713072180646</v>
+        <v>0.04594682917363409</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.8370 ± 0.0234</t>
+          <t>0.5150 ± 0.0459</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.8271 ± 0.0270</t>
+          <t>0.4011 ± 0.0512</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.8275 ± 0.0280</t>
+          <t>0.3448 ± 0.0676</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.8370 ± 0.0234</t>
+          <t>0.5150 ± 0.0459</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.8370 ± 0.0234</t>
+          <t>0.5150 ± 0.0459</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.8271 ± 0.0270</t>
+          <t>0.4011 ± 0.0512</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.8275 ± 0.0280</t>
+          <t>0.3448 ± 0.0676</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>0.8370 ± 0.0234</t>
+          <t>0.5150 ± 0.0459</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>0.728</v>
+        <v>0.3475</v>
       </c>
       <c r="S3" t="n">
-        <v>0.03216278042154384</v>
+        <v>0.05827377912349029</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7495993986021727</v>
+        <v>0.3189944749878827</v>
       </c>
       <c r="U3" t="n">
-        <v>0.02904182696431352</v>
+        <v>0.04955858690316203</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8274841147304658</v>
+        <v>0.3133261472009579</v>
       </c>
       <c r="W3" t="n">
-        <v>0.02375472961573071</v>
+        <v>0.04772700887846521</v>
       </c>
       <c r="X3" t="n">
-        <v>0.728</v>
+        <v>0.3475</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.03216278042154384</v>
+        <v>0.05827377912349029</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.7280 ± 0.0322</t>
+          <t>0.3475 ± 0.0583</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.7496 ± 0.0290</t>
+          <t>0.3190 ± 0.0496</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.8275 ± 0.0238</t>
+          <t>0.3133 ± 0.0477</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>0.7280 ± 0.0322</t>
+          <t>0.3475 ± 0.0583</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0.7280 ± 0.0322</t>
+          <t>0.3475 ± 0.0583</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>0.7496 ± 0.0290</t>
+          <t>0.3190 ± 0.0496</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.8275 ± 0.0238</t>
+          <t>0.3133 ± 0.0477</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.7280 ± 0.0322</t>
+          <t>0.3475 ± 0.0583</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>0.109</v>
+        <v>0.1675</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.07753869615957709</v>
+        <v>0.08210296090955316</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-1.233649202136977e-05</v>
+        <v>0.03146301958379111</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.109</v>
+        <v>0.1675</v>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
@@ -6793,148 +6793,148 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SVM-RBF</t>
+          <t>AdaBoost</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8334999999999999</v>
+        <v>0.515</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01826502425706331</v>
+        <v>0.04887626099538394</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8099526079303931</v>
+        <v>0.4459274392015852</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02569511545306504</v>
+        <v>0.04904546419911374</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8244128167802897</v>
+        <v>0.4204506553904218</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02264298462168463</v>
+        <v>0.07436424082867353</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8334999999999999</v>
+        <v>0.515</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01826502425706331</v>
+        <v>0.04887626099538394</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.8335 ± 0.0183</t>
+          <t>0.5150 ± 0.0489</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.8100 ± 0.0257</t>
+          <t>0.4459 ± 0.0490</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.8244 ± 0.0226</t>
+          <t>0.4205 ± 0.0744</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.8335 ± 0.0183</t>
+          <t>0.5150 ± 0.0489</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.8335 ± 0.0183</t>
+          <t>0.5150 ± 0.0489</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.8100 ± 0.0257</t>
+          <t>0.4459 ± 0.0490</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.8244 ± 0.0226</t>
+          <t>0.4205 ± 0.0744</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.8335 ± 0.0183</t>
+          <t>0.5150 ± 0.0489</t>
         </is>
       </c>
       <c r="R4" t="n">
-        <v>0.7155</v>
+        <v>0.3625</v>
       </c>
       <c r="S4" t="n">
-        <v>0.02278522913351252</v>
+        <v>0.05432668671002207</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7382835601759095</v>
+        <v>0.3313916786357202</v>
       </c>
       <c r="U4" t="n">
-        <v>0.02057169283043969</v>
+        <v>0.04909575685811794</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8183299333627895</v>
+        <v>0.3253566091869237</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0154113579273181</v>
+        <v>0.05303249341597213</v>
       </c>
       <c r="X4" t="n">
-        <v>0.7155</v>
+        <v>0.3625</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.02278522913351252</v>
+        <v>0.05432668671002207</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.7155 ± 0.0228</t>
+          <t>0.3625 ± 0.0543</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.7383 ± 0.0206</t>
+          <t>0.3314 ± 0.0491</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.8183 ± 0.0154</t>
+          <t>0.3254 ± 0.0530</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.7155 ± 0.0228</t>
+          <t>0.3625 ± 0.0543</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0.7155 ± 0.0228</t>
+          <t>0.3625 ± 0.0543</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>0.7383 ± 0.0206</t>
+          <t>0.3314 ± 0.0491</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.8183 ± 0.0154</t>
+          <t>0.3254 ± 0.0530</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.7155 ± 0.0228</t>
+          <t>0.3625 ± 0.0543</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>0.1179999999999999</v>
+        <v>0.1525</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.07166904775448368</v>
+        <v>0.114535760565865</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.006082883417500184</v>
+        <v>0.09509404620349815</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.1179999999999999</v>
+        <v>0.1525</v>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
@@ -6945,148 +6945,148 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GradientBoost</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.833</v>
+        <v>0.5049999999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0240601099101581</v>
+        <v>0.0483045891539648</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8246020797017092</v>
+        <v>0.3946722798843776</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02529261929811836</v>
+        <v>0.05058216691498373</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8239151747889606</v>
+        <v>0.3328350963552577</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02640491712024394</v>
+        <v>0.05354862018695906</v>
       </c>
       <c r="H5" t="n">
-        <v>0.833</v>
+        <v>0.5049999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0240601099101581</v>
+        <v>0.0483045891539648</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.8330 ± 0.0241</t>
+          <t>0.5050 ± 0.0483</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.8246 ± 0.0253</t>
+          <t>0.3947 ± 0.0506</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.8239 ± 0.0264</t>
+          <t>0.3328 ± 0.0535</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.8330 ± 0.0241</t>
+          <t>0.5050 ± 0.0483</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.8330 ± 0.0241</t>
+          <t>0.5050 ± 0.0483</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.8246 ± 0.0253</t>
+          <t>0.3947 ± 0.0506</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.8239 ± 0.0264</t>
+          <t>0.3328 ± 0.0535</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.8330 ± 0.0241</t>
+          <t>0.5050 ± 0.0483</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>0.7785</v>
+        <v>0.3525</v>
       </c>
       <c r="S5" t="n">
-        <v>0.03894797099265179</v>
+        <v>0.06174544517614234</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7931164357496072</v>
+        <v>0.3235520526667839</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03472767570107376</v>
+        <v>0.05209316108357043</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8349204608807771</v>
+        <v>0.3151442410228081</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02494069345512922</v>
+        <v>0.05026454564895595</v>
       </c>
       <c r="X5" t="n">
-        <v>0.7785</v>
+        <v>0.3525</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.03894797099265179</v>
+        <v>0.06174544517614234</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.7785 ± 0.0389</t>
+          <t>0.3525 ± 0.0617</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.7931 ± 0.0347</t>
+          <t>0.3236 ± 0.0521</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.8349 ± 0.0249</t>
+          <t>0.3151 ± 0.0503</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.7785 ± 0.0389</t>
+          <t>0.3525 ± 0.0617</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0.7785 ± 0.0389</t>
+          <t>0.3525 ± 0.0617</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0.7931 ± 0.0347</t>
+          <t>0.3236 ± 0.0521</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.8349 ± 0.0249</t>
+          <t>0.3151 ± 0.0503</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.7785 ± 0.0389</t>
+          <t>0.3525 ± 0.0617</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>0.05449999999999999</v>
+        <v>0.1524999999999999</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.03148564395210196</v>
+        <v>0.0711202272175937</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.0110052860918165</v>
+        <v>0.01769085533244952</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.05449999999999999</v>
+        <v>0.1524999999999999</v>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
@@ -7097,148 +7097,148 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.828</v>
+        <v>0.4875</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02175622516277427</v>
+        <v>0.06373774391990981</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8104028939447145</v>
+        <v>0.4637476319006376</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02627109794847402</v>
+        <v>0.06802787926675574</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8146192868859166</v>
+        <v>0.4624339081811907</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02793976606486409</v>
+        <v>0.07612364353088311</v>
       </c>
       <c r="H6" t="n">
-        <v>0.828</v>
+        <v>0.4875</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02175622516277427</v>
+        <v>0.06373774391990981</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.8280 ± 0.0218</t>
+          <t>0.4875 ± 0.0637</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.8104 ± 0.0263</t>
+          <t>0.4637 ± 0.0680</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.8146 ± 0.0279</t>
+          <t>0.4624 ± 0.0761</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>0.8280 ± 0.0218</t>
+          <t>0.4875 ± 0.0637</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.8280 ± 0.0218</t>
+          <t>0.4875 ± 0.0637</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.8104 ± 0.0263</t>
+          <t>0.4637 ± 0.0680</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.8146 ± 0.0279</t>
+          <t>0.4624 ± 0.0761</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>0.8280 ± 0.0218</t>
+          <t>0.4875 ± 0.0637</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>0.7204999999999999</v>
+        <v>0.3875</v>
       </c>
       <c r="S6" t="n">
-        <v>0.02521573582771946</v>
+        <v>0.04602233757161359</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7425816669128837</v>
+        <v>0.352540310813392</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0226289966124321</v>
+        <v>0.03715017862020168</v>
       </c>
       <c r="V6" t="n">
-        <v>0.8168901353561694</v>
+        <v>0.3376487727398011</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0142346735725995</v>
+        <v>0.03098537518318151</v>
       </c>
       <c r="X6" t="n">
-        <v>0.7204999999999999</v>
+        <v>0.3875</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.02521573582771946</v>
+        <v>0.04602233757161359</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.7205 ± 0.0252</t>
+          <t>0.3875 ± 0.0460</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.7426 ± 0.0226</t>
+          <t>0.3525 ± 0.0372</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.8169 ± 0.0142</t>
+          <t>0.3376 ± 0.0310</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>0.7205 ± 0.0252</t>
+          <t>0.3875 ± 0.0460</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0.7205 ± 0.0252</t>
+          <t>0.3875 ± 0.0460</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>0.7426 ± 0.0226</t>
+          <t>0.3525 ± 0.0372</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.8169 ± 0.0142</t>
+          <t>0.3376 ± 0.0310</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>0.7205 ± 0.0252</t>
+          <t>0.3875 ± 0.0460</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>0.1075</v>
+        <v>0.09999999999999998</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.0678212270318308</v>
+        <v>0.1112073210872455</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.002270848470252829</v>
+        <v>0.1247851354413896</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.1075</v>
+        <v>0.09999999999999998</v>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
@@ -7249,148 +7249,148 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ExtraTrees</t>
+          <t>NaiveBayes</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8240000000000001</v>
+        <v>0.485</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02469817807045691</v>
+        <v>0.05797509043642027</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8177052906725901</v>
+        <v>0.3884614332892806</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02578592983226878</v>
+        <v>0.04926617125562362</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8164120745306315</v>
+        <v>0.3748825660014655</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02647286138062653</v>
+        <v>0.103253106459303</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8240000000000001</v>
+        <v>0.485</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02469817807045691</v>
+        <v>0.05797509043642027</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.8240 ± 0.0247</t>
+          <t>0.4850 ± 0.0580</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.8177 ± 0.0258</t>
+          <t>0.3885 ± 0.0493</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.8164 ± 0.0265</t>
+          <t>0.3749 ± 0.1033</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.8240 ± 0.0247</t>
+          <t>0.4850 ± 0.0580</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.8240 ± 0.0247</t>
+          <t>0.4850 ± 0.0580</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.8177 ± 0.0258</t>
+          <t>0.3885 ± 0.0493</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.8164 ± 0.0265</t>
+          <t>0.3749 ± 0.1033</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.8240 ± 0.0247</t>
+          <t>0.4850 ± 0.0580</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>0.7175</v>
+        <v>0.4525</v>
       </c>
       <c r="S7" t="n">
-        <v>0.02359967043084385</v>
+        <v>0.03987828704668466</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7398815798072279</v>
+        <v>0.3424611813376494</v>
       </c>
       <c r="U7" t="n">
-        <v>0.02149208500894103</v>
+        <v>0.02934375406805491</v>
       </c>
       <c r="V7" t="n">
-        <v>0.8160294753040294</v>
+        <v>0.2819780181439633</v>
       </c>
       <c r="W7" t="n">
-        <v>0.02063605637657615</v>
+        <v>0.03061914893120251</v>
       </c>
       <c r="X7" t="n">
-        <v>0.7175</v>
+        <v>0.4525</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.02359967043084385</v>
+        <v>0.03987828704668466</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.7175 ± 0.0236</t>
+          <t>0.4525 ± 0.0399</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.7399 ± 0.0215</t>
+          <t>0.3425 ± 0.0293</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.8160 ± 0.0206</t>
+          <t>0.2820 ± 0.0306</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>0.7175 ± 0.0236</t>
+          <t>0.4525 ± 0.0399</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0.7175 ± 0.0236</t>
+          <t>0.4525 ± 0.0399</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>0.7399 ± 0.0215</t>
+          <t>0.3425 ± 0.0293</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.8160 ± 0.0206</t>
+          <t>0.2820 ± 0.0306</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>0.7175 ± 0.0236</t>
+          <t>0.4525 ± 0.0399</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>0.1065</v>
+        <v>0.03250000000000008</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.07782371086536222</v>
+        <v>0.04600025195163115</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.0003825992266021094</v>
+        <v>0.09290454785750213</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.1065</v>
+        <v>0.03250000000000008</v>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
@@ -7401,148 +7401,148 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NaiveBayes</t>
+          <t>ExtraTrees</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8090000000000002</v>
+        <v>0.4774999999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02579836342785244</v>
+        <v>0.06503204338375557</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7856952309335539</v>
+        <v>0.4691265033149707</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02992064254649245</v>
+        <v>0.06795290437956898</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7897580695297388</v>
+        <v>0.4692555641821946</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03856477005414511</v>
+        <v>0.07472771724947783</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8090000000000002</v>
+        <v>0.4774999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02579836342785244</v>
+        <v>0.06503204338375557</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.8090 ± 0.0258</t>
+          <t>0.4775 ± 0.0650</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.7857 ± 0.0299</t>
+          <t>0.4691 ± 0.0680</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.7898 ± 0.0386</t>
+          <t>0.4693 ± 0.0747</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.8090 ± 0.0258</t>
+          <t>0.4775 ± 0.0650</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.8090 ± 0.0258</t>
+          <t>0.4775 ± 0.0650</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.7857 ± 0.0299</t>
+          <t>0.4691 ± 0.0680</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.7898 ± 0.0386</t>
+          <t>0.4693 ± 0.0747</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.8090 ± 0.0258</t>
+          <t>0.4775 ± 0.0650</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>0.7725000000000002</v>
+        <v>0.37</v>
       </c>
       <c r="S8" t="n">
-        <v>0.02821051813301795</v>
+        <v>0.05627314338711378</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7665686732006363</v>
+        <v>0.3362847653287579</v>
       </c>
       <c r="U8" t="n">
-        <v>0.02814661533497105</v>
+        <v>0.0482375805332325</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7632603404979916</v>
+        <v>0.3247934755900835</v>
       </c>
       <c r="W8" t="n">
-        <v>0.02924767136212271</v>
+        <v>0.03788690753218912</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7725000000000002</v>
+        <v>0.37</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.02821051813301795</v>
+        <v>0.05627314338711378</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.7725 ± 0.0282</t>
+          <t>0.3700 ± 0.0563</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.7666 ± 0.0281</t>
+          <t>0.3363 ± 0.0482</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.7633 ± 0.0292</t>
+          <t>0.3248 ± 0.0379</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>0.7725 ± 0.0282</t>
+          <t>0.3700 ± 0.0563</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0.7725 ± 0.0282</t>
+          <t>0.3700 ± 0.0563</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>0.7666 ± 0.0281</t>
+          <t>0.3363 ± 0.0482</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.7633 ± 0.0292</t>
+          <t>0.3248 ± 0.0379</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>0.7725 ± 0.0282</t>
+          <t>0.3700 ± 0.0563</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>0.03649999999999998</v>
+        <v>0.1074999999999999</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.0191265577329176</v>
+        <v>0.1328417379862128</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.02649772903174719</v>
+        <v>0.1444620885921111</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.03649999999999998</v>
+        <v>0.1074999999999999</v>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
@@ -7553,148 +7553,148 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MLP</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8074999999999999</v>
+        <v>0.4699999999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02552232138518923</v>
+        <v>0.07799572637865058</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8069554910760722</v>
+        <v>0.4464738356606046</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02380568201797918</v>
+        <v>0.07281623112317112</v>
       </c>
       <c r="F9" t="n">
-        <v>0.808348378171001</v>
+        <v>0.4380473084886128</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02217982684553994</v>
+        <v>0.08049181275833353</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8074999999999999</v>
+        <v>0.4699999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02552232138518923</v>
+        <v>0.07799572637865058</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.8075 ± 0.0255</t>
+          <t>0.4700 ± 0.0780</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.8070 ± 0.0238</t>
+          <t>0.4465 ± 0.0728</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.8083 ± 0.0222</t>
+          <t>0.4380 ± 0.0805</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.8075 ± 0.0255</t>
+          <t>0.4700 ± 0.0780</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.8075 ± 0.0255</t>
+          <t>0.4700 ± 0.0780</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.8070 ± 0.0238</t>
+          <t>0.4465 ± 0.0728</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.8083 ± 0.0222</t>
+          <t>0.4380 ± 0.0805</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.8075 ± 0.0255</t>
+          <t>0.4700 ± 0.0780</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>0.7040000000000001</v>
+        <v>0.3625</v>
       </c>
       <c r="S9" t="n">
-        <v>0.03680277767294805</v>
+        <v>0.05432668671002207</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7272345527266039</v>
+        <v>0.323682382109807</v>
       </c>
       <c r="U9" t="n">
-        <v>0.03311353328519049</v>
+        <v>0.04715637281918291</v>
       </c>
       <c r="V9" t="n">
-        <v>0.8053433697361732</v>
+        <v>0.3125416400433184</v>
       </c>
       <c r="W9" t="n">
-        <v>0.01971851560894098</v>
+        <v>0.04310884461312551</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7040000000000001</v>
+        <v>0.3625</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.03680277767294805</v>
+        <v>0.05432668671002207</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.7040 ± 0.0368</t>
+          <t>0.3625 ± 0.0543</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.7272 ± 0.0331</t>
+          <t>0.3237 ± 0.0472</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.8053 ± 0.0197</t>
+          <t>0.3125 ± 0.0431</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0.7040 ± 0.0368</t>
+          <t>0.3625 ± 0.0543</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0.7040 ± 0.0368</t>
+          <t>0.3625 ± 0.0543</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>0.7272 ± 0.0331</t>
+          <t>0.3237 ± 0.0472</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.8053 ± 0.0197</t>
+          <t>0.3125 ± 0.0431</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>0.7040 ± 0.0368</t>
+          <t>0.3625 ± 0.0543</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>0.1034999999999998</v>
+        <v>0.1074999999999999</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.07972093834946836</v>
+        <v>0.1227914535507976</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.003005008434827872</v>
+        <v>0.1255056684452944</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.1034999999999998</v>
+        <v>0.1074999999999999</v>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
@@ -7705,148 +7705,148 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>MLP</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8069999999999998</v>
+        <v>0.4275</v>
       </c>
       <c r="C10" t="n">
-        <v>0.02250925735484548</v>
+        <v>0.05945352993912324</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8008786340418022</v>
+        <v>0.420859292671839</v>
       </c>
       <c r="E10" t="n">
-        <v>0.02509907434611157</v>
+        <v>0.0582664427371178</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7978462200616508</v>
+        <v>0.4272267905705405</v>
       </c>
       <c r="G10" t="n">
-        <v>0.02661462081347623</v>
+        <v>0.06077100676915963</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8069999999999998</v>
+        <v>0.4275</v>
       </c>
       <c r="I10" t="n">
-        <v>0.02250925735484548</v>
+        <v>0.05945352993912324</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.8070 ± 0.0225</t>
+          <t>0.4275 ± 0.0595</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.8009 ± 0.0251</t>
+          <t>0.4209 ± 0.0583</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.7978 ± 0.0266</t>
+          <t>0.4272 ± 0.0608</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.8070 ± 0.0225</t>
+          <t>0.4275 ± 0.0595</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.8070 ± 0.0225</t>
+          <t>0.4275 ± 0.0595</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.8009 ± 0.0251</t>
+          <t>0.4209 ± 0.0583</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.7978 ± 0.0266</t>
+          <t>0.4272 ± 0.0608</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.8070 ± 0.0225</t>
+          <t>0.4275 ± 0.0595</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>0.6819999999999999</v>
+        <v>0.375</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0204396129556745</v>
+        <v>0.05270462766947298</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7079182364756985</v>
+        <v>0.3417448998020196</v>
       </c>
       <c r="U10" t="n">
-        <v>0.01875433200562023</v>
+        <v>0.04423250905732919</v>
       </c>
       <c r="V10" t="n">
-        <v>0.8002301847805896</v>
+        <v>0.3347121761089152</v>
       </c>
       <c r="W10" t="n">
-        <v>0.01929628218260107</v>
+        <v>0.04258883152100918</v>
       </c>
       <c r="X10" t="n">
-        <v>0.6819999999999999</v>
+        <v>0.375</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.0204396129556745</v>
+        <v>0.05270462766947298</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.6820 ± 0.0204</t>
+          <t>0.3750 ± 0.0527</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.7079 ± 0.0188</t>
+          <t>0.3417 ± 0.0442</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.8002 ± 0.0193</t>
+          <t>0.3347 ± 0.0426</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>0.6820 ± 0.0204</t>
+          <t>0.3750 ± 0.0527</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0.6820 ± 0.0204</t>
+          <t>0.3750 ± 0.0527</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>0.7079 ± 0.0188</t>
+          <t>0.3417 ± 0.0442</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.8002 ± 0.0193</t>
+          <t>0.3347 ± 0.0426</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>0.6820 ± 0.0204</t>
+          <t>0.3750 ± 0.0527</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>0.1249999999999999</v>
+        <v>0.05250000000000005</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.09296039756610364</v>
+        <v>0.07911439286981942</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0.002383964718938758</v>
+        <v>0.09251461446162529</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.1249999999999999</v>
+        <v>0.05250000000000005</v>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
@@ -7861,144 +7861,144 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.784</v>
+        <v>0.4175</v>
       </c>
       <c r="C11" t="n">
-        <v>0.02913569784454954</v>
+        <v>0.0601502747753953</v>
       </c>
       <c r="D11" t="n">
-        <v>0.785293092246484</v>
+        <v>0.4187416830432881</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02860525768452616</v>
+        <v>0.05976891793014379</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7880825733490411</v>
+        <v>0.4405900453712953</v>
       </c>
       <c r="G11" t="n">
-        <v>0.02887004930408354</v>
+        <v>0.06784141632447085</v>
       </c>
       <c r="H11" t="n">
-        <v>0.784</v>
+        <v>0.4175</v>
       </c>
       <c r="I11" t="n">
-        <v>0.02913569784454954</v>
+        <v>0.0601502747753953</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.7840 ± 0.0291</t>
+          <t>0.4175 ± 0.0602</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.7853 ± 0.0286</t>
+          <t>0.4187 ± 0.0598</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.7881 ± 0.0289</t>
+          <t>0.4406 ± 0.0678</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.7840 ± 0.0291</t>
+          <t>0.4175 ± 0.0602</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.7840 ± 0.0291</t>
+          <t>0.4175 ± 0.0602</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.7853 ± 0.0286</t>
+          <t>0.4187 ± 0.0598</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.7881 ± 0.0289</t>
+          <t>0.4406 ± 0.0678</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.7840 ± 0.0291</t>
+          <t>0.4175 ± 0.0602</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>0.6325</v>
+        <v>0.3875000000000001</v>
       </c>
       <c r="S11" t="n">
-        <v>0.04104536785341586</v>
+        <v>0.06263873490988711</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6618426726971874</v>
+        <v>0.3441634354530214</v>
       </c>
       <c r="U11" t="n">
-        <v>0.03707232762900146</v>
+        <v>0.05281902859808141</v>
       </c>
       <c r="V11" t="n">
-        <v>0.7511015945240864</v>
+        <v>0.327384385984635</v>
       </c>
       <c r="W11" t="n">
-        <v>0.02425709812870806</v>
+        <v>0.04551896719438788</v>
       </c>
       <c r="X11" t="n">
-        <v>0.6325000000000001</v>
+        <v>0.3875000000000001</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.04104536785341584</v>
+        <v>0.06263873490988711</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.6325 ± 0.0410</t>
+          <t>0.3875 ± 0.0626</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.6618 ± 0.0371</t>
+          <t>0.3442 ± 0.0528</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.7511 ± 0.0243</t>
+          <t>0.3274 ± 0.0455</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>0.6325 ± 0.0410</t>
+          <t>0.3875 ± 0.0626</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0.6325 ± 0.0410</t>
+          <t>0.3875 ± 0.0626</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>0.6618 ± 0.0371</t>
+          <t>0.3442 ± 0.0528</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.7511 ± 0.0243</t>
+          <t>0.3274 ± 0.0455</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0.6325 ± 0.0410</t>
+          <t>0.3875 ± 0.0626</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>0.1515000000000001</v>
+        <v>0.02999999999999992</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.1234504195492966</v>
+        <v>0.07457824759026677</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.03698097882495466</v>
+        <v>0.1132056593866603</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.1515</v>
+        <v>0.02999999999999992</v>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
